--- a/03_Outputs/all/03_DS/ds_idx10_juventud.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx10_juventud.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.05824908798864</v>
+        <v>2.058249087988643</v>
       </c>
       <c r="D2">
         <v>-1.145109845431552</v>
       </c>
       <c r="E2">
-        <v>-0.4288595452115392</v>
+        <v>-0.4288595452115398</v>
       </c>
       <c r="F2">
-        <v>-0.3960634271100612</v>
+        <v>-0.3960634271100602</v>
       </c>
       <c r="G2">
-        <v>0.51361849845588</v>
+        <v>0.5136184984558807</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.5068052052360653</v>
+        <v>-0.5068052052360665</v>
       </c>
       <c r="D3">
-        <v>1.233262103925826</v>
+        <v>1.233262103925824</v>
       </c>
       <c r="E3">
-        <v>0.6099211008706619</v>
+        <v>0.6099211008706608</v>
       </c>
       <c r="F3">
-        <v>-0.146404062910288</v>
+        <v>-0.1464040629102908</v>
       </c>
       <c r="G3">
-        <v>-0.4953117318819946</v>
+        <v>-0.4953117318819929</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4253190302663227</v>
+        <v>0.4253190302663208</v>
       </c>
       <c r="D4">
         <v>3.00744586847724</v>
       </c>
       <c r="E4">
-        <v>1.403944349525695</v>
+        <v>1.403944349525694</v>
       </c>
       <c r="F4">
-        <v>-0.3349251825504378</v>
+        <v>-0.3349251825504388</v>
       </c>
       <c r="G4">
-        <v>0.09842897848026685</v>
+        <v>0.09842897848026916</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.5853826321693281</v>
+        <v>0.585382632169328</v>
       </c>
       <c r="D5">
-        <v>1.779718760704281</v>
+        <v>1.779718760704279</v>
       </c>
       <c r="E5">
-        <v>-0.8116316221226425</v>
+        <v>-0.8116316221226437</v>
       </c>
       <c r="F5">
-        <v>-1.056767516931018</v>
+        <v>-1.056767516931022</v>
       </c>
       <c r="G5">
-        <v>-0.865526772087946</v>
+        <v>-0.8655267720879434</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.8414813909967307</v>
+        <v>0.8414813909967314</v>
       </c>
       <c r="D6">
         <v>-0.2902292231515735</v>
       </c>
       <c r="E6">
-        <v>0.907516068586944</v>
+        <v>0.9075160685869437</v>
       </c>
       <c r="F6">
-        <v>0.7996414897689531</v>
+        <v>0.7996414897689496</v>
       </c>
       <c r="G6">
-        <v>-0.9893101061250988</v>
+        <v>-0.9893101061251013</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3617624276915839</v>
+        <v>-0.3617624276915842</v>
       </c>
       <c r="D7">
-        <v>1.620643623449948</v>
+        <v>1.620643623449947</v>
       </c>
       <c r="E7">
-        <v>0.6071197162182534</v>
+        <v>0.6071197162182528</v>
       </c>
       <c r="F7">
-        <v>0.1216380661047777</v>
+        <v>0.1216380661047786</v>
       </c>
       <c r="G7">
-        <v>0.7743877549468827</v>
+        <v>0.7743877549468825</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.8624132329466492</v>
+        <v>0.8624132329466511</v>
       </c>
       <c r="D8">
-        <v>-0.4657998740679062</v>
+        <v>-0.465799874067906</v>
       </c>
       <c r="E8">
-        <v>0.6327464860405841</v>
+        <v>0.6327464860405835</v>
       </c>
       <c r="F8">
-        <v>0.1647331027387875</v>
+        <v>0.164733102738788</v>
       </c>
       <c r="G8">
-        <v>0.2247995565871122</v>
+        <v>0.2247995565871126</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.7789745909031152</v>
+        <v>0.7789745909031167</v>
       </c>
       <c r="D9">
-        <v>0.1889172711791241</v>
+        <v>0.188917271179123</v>
       </c>
       <c r="E9">
-        <v>-1.471454806526665</v>
+        <v>-1.471454806526667</v>
       </c>
       <c r="F9">
-        <v>-0.02652557400423457</v>
+        <v>-0.02652557400423824</v>
       </c>
       <c r="G9">
-        <v>-1.037015789269913</v>
+        <v>-1.037015789269914</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-1.294546914989526</v>
+        <v>-1.294546914989528</v>
       </c>
       <c r="D10">
-        <v>2.483826555023261</v>
+        <v>2.483826555023258</v>
       </c>
       <c r="E10">
-        <v>0.07146957871475904</v>
+        <v>0.07146957871475745</v>
       </c>
       <c r="F10">
-        <v>-0.8976782121991183</v>
+        <v>-0.8976782121991224</v>
       </c>
       <c r="G10">
-        <v>-0.8020781549381016</v>
+        <v>-0.8020781549380969</v>
       </c>
     </row>
     <row r="11">
@@ -649,16 +649,16 @@
         <v>-2.74233717358236</v>
       </c>
       <c r="D11">
-        <v>1.86398569328124</v>
+        <v>1.863985693281235</v>
       </c>
       <c r="E11">
-        <v>1.240164242497328</v>
+        <v>1.240164242497325</v>
       </c>
       <c r="F11">
-        <v>-2.020892827299461</v>
+        <v>-2.020892827299455</v>
       </c>
       <c r="G11">
-        <v>2.373844224158861</v>
+        <v>2.373844224158865</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.1842835290951245</v>
+        <v>0.1842835290951261</v>
       </c>
       <c r="D12">
-        <v>-0.5269721099026294</v>
+        <v>-0.5269721099026301</v>
       </c>
       <c r="E12">
-        <v>-0.2346104841867927</v>
+        <v>-0.2346104841867937</v>
       </c>
       <c r="F12">
-        <v>0.8336513251081433</v>
+        <v>0.833651325108142</v>
       </c>
       <c r="G12">
-        <v>-0.6352297699373923</v>
+        <v>-0.6352297699373944</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-1.265555569106476</v>
+        <v>-1.265555569106477</v>
       </c>
       <c r="D13">
-        <v>1.130788815213391</v>
+        <v>1.130788815213389</v>
       </c>
       <c r="E13">
-        <v>-0.003324701227665483</v>
+        <v>-0.00332470122766689</v>
       </c>
       <c r="F13">
-        <v>-0.6475321466941352</v>
+        <v>-0.6475321466941368</v>
       </c>
       <c r="G13">
-        <v>-0.3585707796121361</v>
+        <v>-0.3585707796121328</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.2844862543937529</v>
+        <v>0.2844862543937555</v>
       </c>
       <c r="D14">
-        <v>-1.190695441170869</v>
+        <v>-1.190695441170871</v>
       </c>
       <c r="E14">
-        <v>-0.9408260125310041</v>
+        <v>-0.940826012531005</v>
       </c>
       <c r="F14">
-        <v>0.9336525919571139</v>
+        <v>0.9336525919571101</v>
       </c>
       <c r="G14">
-        <v>-1.026575510571309</v>
+        <v>-1.026575510571312</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-1.614332701556932</v>
+        <v>-1.614332701556931</v>
       </c>
       <c r="D15">
-        <v>-0.9621181694679198</v>
+        <v>-0.9621181694679224</v>
       </c>
       <c r="E15">
-        <v>-1.529450066586518</v>
+        <v>-1.529450066586521</v>
       </c>
       <c r="F15">
-        <v>0.1958955179460132</v>
+        <v>0.1958955179460102</v>
       </c>
       <c r="G15">
-        <v>-0.8790457259246608</v>
+        <v>-0.87904572592466</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.3863560396020246</v>
+        <v>-0.386356039602025</v>
       </c>
       <c r="D16">
-        <v>1.218348315876946</v>
+        <v>1.218348315876945</v>
       </c>
       <c r="E16">
-        <v>0.8798151094800328</v>
+        <v>0.8798151094800321</v>
       </c>
       <c r="F16">
-        <v>-0.5192689687688155</v>
+        <v>-0.5192689687688168</v>
       </c>
       <c r="G16">
-        <v>-0.160688792480056</v>
+        <v>-0.160688792480052</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>2.088471510816315</v>
+        <v>2.088471510816313</v>
       </c>
       <c r="D17">
-        <v>0.2436358508995268</v>
+        <v>0.2436358508995303</v>
       </c>
       <c r="E17">
         <v>3.521512584613645</v>
       </c>
       <c r="F17">
-        <v>2.479969991418781</v>
+        <v>2.479969991418783</v>
       </c>
       <c r="G17">
-        <v>-0.1303712913791772</v>
+        <v>-0.1303712913791851</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.5306993040950709</v>
+        <v>0.530699304095071</v>
       </c>
       <c r="D18">
-        <v>-0.2196798828375013</v>
+        <v>-0.2196798828375017</v>
       </c>
       <c r="E18">
-        <v>0.802622178319391</v>
+        <v>0.8026221783193906</v>
       </c>
       <c r="F18">
-        <v>-0.3726227021013578</v>
+        <v>-0.3726227021013605</v>
       </c>
       <c r="G18">
-        <v>-0.5058920371418997</v>
+        <v>-0.5058920371418982</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.2001214749253011</v>
+        <v>-0.2001214749253008</v>
       </c>
       <c r="D19">
-        <v>0.6526351195727915</v>
+        <v>0.6526351195727895</v>
       </c>
       <c r="E19">
-        <v>-1.174503492586415</v>
+        <v>-1.174503492586416</v>
       </c>
       <c r="F19">
-        <v>-0.149594301647811</v>
+        <v>-0.1495943016478149</v>
       </c>
       <c r="G19">
-        <v>-0.9457259992549962</v>
+        <v>-0.9457259992549956</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>2.07422887929489</v>
+        <v>2.074228879294891</v>
       </c>
       <c r="D20">
-        <v>-1.139778415254324</v>
+        <v>-1.139778415254322</v>
       </c>
       <c r="E20">
-        <v>0.6191188357119725</v>
+        <v>0.6191188357119722</v>
       </c>
       <c r="F20">
-        <v>0.04096825081684998</v>
+        <v>0.0409682508168513</v>
       </c>
       <c r="G20">
-        <v>0.5400913572107009</v>
+        <v>0.5400913572107005</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.1448754713018365</v>
+        <v>-0.1448754713018373</v>
       </c>
       <c r="D21">
         <v>2.800282792255279</v>
       </c>
       <c r="E21">
-        <v>0.9663164572967704</v>
+        <v>0.9663164572967696</v>
       </c>
       <c r="F21">
-        <v>0.5116412062982887</v>
+        <v>0.5116412062982862</v>
       </c>
       <c r="G21">
-        <v>-0.4216575077996145</v>
+        <v>-0.421657507799614</v>
       </c>
     </row>
     <row r="22">
@@ -946,16 +946,16 @@
         <v>-1.626182200666803</v>
       </c>
       <c r="D22">
-        <v>0.9428886337010201</v>
+        <v>0.9428886337010174</v>
       </c>
       <c r="E22">
-        <v>0.8525505683527559</v>
+        <v>0.852550568352754</v>
       </c>
       <c r="F22">
-        <v>-0.4231102475630862</v>
+        <v>-0.4231102475630861</v>
       </c>
       <c r="G22">
-        <v>0.3062939313102175</v>
+        <v>0.3062939313102174</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.619572964645912</v>
+        <v>0.6195729646459136</v>
       </c>
       <c r="D23">
-        <v>-2.425587590503659</v>
+        <v>-2.425587590503658</v>
       </c>
       <c r="E23">
         <v>2.035125509596694</v>
       </c>
       <c r="F23">
-        <v>-0.587063499362194</v>
+        <v>-0.5870634993621958</v>
       </c>
       <c r="G23">
-        <v>-0.6251378811181978</v>
+        <v>-0.6251378811181951</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-2.253205315108043</v>
+        <v>-2.25320531510804</v>
       </c>
       <c r="D24">
-        <v>1.964817633971208</v>
+        <v>1.964817633971202</v>
       </c>
       <c r="E24">
-        <v>0.1024598502103235</v>
+        <v>0.1024598502103197</v>
       </c>
       <c r="F24">
-        <v>-1.753798077879994</v>
+        <v>-1.753798077879982</v>
       </c>
       <c r="G24">
-        <v>4.56581331793585</v>
+        <v>4.565813317935849</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.7831651658024225</v>
+        <v>-0.7831651658024216</v>
       </c>
       <c r="D25">
-        <v>-1.06780611482473</v>
+        <v>-1.067806114824731</v>
       </c>
       <c r="E25">
-        <v>1.703471816879341</v>
+        <v>1.703471816879339</v>
       </c>
       <c r="F25">
-        <v>-1.503175106791938</v>
+        <v>-1.503175106791936</v>
       </c>
       <c r="G25">
-        <v>0.5557158155561994</v>
+        <v>0.5557158155562067</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-1.769609914411628</v>
+        <v>-1.769609914411626</v>
       </c>
       <c r="D26">
-        <v>-0.7239542878979489</v>
+        <v>-0.7239542878979516</v>
       </c>
       <c r="E26">
-        <v>-0.03931769878749278</v>
+        <v>-0.03931769878749445</v>
       </c>
       <c r="F26">
-        <v>0.3194689641440426</v>
+        <v>0.3194689641440414</v>
       </c>
       <c r="G26">
-        <v>-0.2075722292496756</v>
+        <v>-0.2075722292496757</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.143154310363568</v>
+        <v>-0.1431543103635687</v>
       </c>
       <c r="D27">
-        <v>1.829802812615973</v>
+        <v>1.82980281261597</v>
       </c>
       <c r="E27">
-        <v>-2.15513310668851</v>
+        <v>-2.155133106688512</v>
       </c>
       <c r="F27">
-        <v>-1.675919296349386</v>
+        <v>-1.675919296349388</v>
       </c>
       <c r="G27">
-        <v>-0.3258738924277498</v>
+        <v>-0.3258738924277445</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>1.928618899158614</v>
+        <v>1.928618899158616</v>
       </c>
       <c r="D28">
-        <v>-2.079604297857431</v>
+        <v>-2.07960429785743</v>
       </c>
       <c r="E28">
-        <v>0.8502072921281247</v>
+        <v>0.8502072921281248</v>
       </c>
       <c r="F28">
-        <v>-1.578527430082854</v>
+        <v>-1.578527430082852</v>
       </c>
       <c r="G28">
-        <v>1.27476598259894</v>
+        <v>1.274765982598945</v>
       </c>
     </row>
     <row r="29">
@@ -1135,16 +1135,16 @@
         <v>-1.980020246958708</v>
       </c>
       <c r="D29">
-        <v>3.276335353356726</v>
+        <v>3.276335353356722</v>
       </c>
       <c r="E29">
-        <v>0.5080004178327641</v>
+        <v>0.5080004178327607</v>
       </c>
       <c r="F29">
-        <v>-0.0517064198744274</v>
+        <v>-0.05170641987441976</v>
       </c>
       <c r="G29">
-        <v>2.57025284117806</v>
+        <v>2.570252841178055</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.2977939065118242</v>
+        <v>-0.2977939065118249</v>
       </c>
       <c r="D30">
-        <v>0.9253589583929845</v>
+        <v>0.9253589583929829</v>
       </c>
       <c r="E30">
-        <v>-0.56173549989961</v>
+        <v>-0.5617354998996114</v>
       </c>
       <c r="F30">
-        <v>-0.543606579764331</v>
+        <v>-0.5436065797643344</v>
       </c>
       <c r="G30">
-        <v>-0.8038284038777741</v>
+        <v>-0.8038284038777723</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.6311532344334703</v>
+        <v>0.6311532344334724</v>
       </c>
       <c r="D31">
-        <v>0.359264005874203</v>
+        <v>0.3592640058742014</v>
       </c>
       <c r="E31">
-        <v>-1.91437279868312</v>
+        <v>-1.914372798683122</v>
       </c>
       <c r="F31">
-        <v>-1.34293002348594</v>
+        <v>-1.342930023485941</v>
       </c>
       <c r="G31">
-        <v>-0.2771162169650037</v>
+        <v>-0.2771162169649992</v>
       </c>
     </row>
     <row r="32">
@@ -1213,16 +1213,16 @@
         </is>
       </c>
       <c r="C32">
-        <v>-1.567404970396689</v>
+        <v>-1.56740497039669</v>
       </c>
       <c r="D32">
-        <v>1.529079586820325</v>
+        <v>1.529079586820322</v>
       </c>
       <c r="E32">
-        <v>-0.746761112234906</v>
+        <v>-0.7467611122349074</v>
       </c>
       <c r="F32">
-        <v>0.5881646765324756</v>
+        <v>0.5881646765324703</v>
       </c>
       <c r="G32">
         <v>-1.237414127267997</v>
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.5457671558375859</v>
+        <v>-0.5457671558375843</v>
       </c>
       <c r="D33">
-        <v>-0.2510535500074308</v>
+        <v>-0.2510535500074325</v>
       </c>
       <c r="E33">
-        <v>-1.133237566489231</v>
+        <v>-1.133237566489232</v>
       </c>
       <c r="F33">
-        <v>1.535237938391889</v>
+        <v>1.535237938391886</v>
       </c>
       <c r="G33">
-        <v>-0.965883654716955</v>
+        <v>-0.9658836547169591</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.953452427282498</v>
+        <v>1.953452427282499</v>
       </c>
       <c r="D34">
-        <v>-0.6470429154051653</v>
+        <v>-0.6470429154051638</v>
       </c>
       <c r="E34">
-        <v>0.6475747286190682</v>
+        <v>0.6475747286190677</v>
       </c>
       <c r="F34">
-        <v>-0.2665285542580265</v>
+        <v>-0.2665285542580233</v>
       </c>
       <c r="G34">
-        <v>1.118990819595223</v>
+        <v>1.118990819595224</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.1363657164759426</v>
+        <v>-0.1363657164759434</v>
       </c>
       <c r="D35">
         <v>1.365960602690794</v>
       </c>
       <c r="E35">
-        <v>1.010561562919571</v>
+        <v>1.01056156291957</v>
       </c>
       <c r="F35">
-        <v>0.551306029018085</v>
+        <v>0.5513060290180831</v>
       </c>
       <c r="G35">
-        <v>-0.4850137493422468</v>
+        <v>-0.4850137493422474</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.4545623172232863</v>
+        <v>0.4545623172232885</v>
       </c>
       <c r="D36">
-        <v>-1.22523427859248</v>
+        <v>-1.225234278592479</v>
       </c>
       <c r="E36">
-        <v>-0.2113803167704807</v>
+        <v>-0.2113803167704824</v>
       </c>
       <c r="F36">
-        <v>1.36522568152277</v>
+        <v>1.365225681522773</v>
       </c>
       <c r="G36">
-        <v>0.7691323420353422</v>
+        <v>0.7691323420353381</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-1.695562818408903</v>
+        <v>-1.695562818408902</v>
       </c>
       <c r="D37">
-        <v>-1.177504317991539</v>
+        <v>-1.177504317991542</v>
       </c>
       <c r="E37">
-        <v>-0.01773229839838538</v>
+        <v>-0.01773229839838623</v>
       </c>
       <c r="F37">
-        <v>0.5651414800585965</v>
+        <v>0.5651414800585901</v>
       </c>
       <c r="G37">
-        <v>-1.563032319621477</v>
+        <v>-1.563032319621478</v>
       </c>
     </row>
     <row r="38">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.4305801649955913</v>
+        <v>-0.4305801649955896</v>
       </c>
       <c r="D38">
-        <v>-0.5168224425206501</v>
+        <v>-0.5168224425206518</v>
       </c>
       <c r="E38">
-        <v>0.4914047360483502</v>
+        <v>0.4914047360483497</v>
       </c>
       <c r="F38">
-        <v>0.468642405273864</v>
+        <v>0.4686424052738588</v>
       </c>
       <c r="G38">
         <v>-1.304517887011377</v>
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.4222122626689938</v>
+        <v>0.4222122626689951</v>
       </c>
       <c r="D39">
-        <v>-0.6107710622258942</v>
+        <v>-0.6107710622258953</v>
       </c>
       <c r="E39">
-        <v>-0.6598718140173239</v>
+        <v>-0.6598718140173243</v>
       </c>
       <c r="F39">
-        <v>-1.298946595367538</v>
+        <v>-1.298946595367539</v>
       </c>
       <c r="G39">
-        <v>0.1049860403969251</v>
+        <v>0.1049860403969301</v>
       </c>
     </row>
     <row r="40">
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.1325799175405034</v>
+        <v>0.1325799175405022</v>
       </c>
       <c r="D40">
-        <v>3.002223353072305</v>
+        <v>3.002223353072304</v>
       </c>
       <c r="E40">
-        <v>-0.6868565622996836</v>
+        <v>-0.6868565622996844</v>
       </c>
       <c r="F40">
-        <v>0.01115939311717096</v>
+        <v>0.01115939311716622</v>
       </c>
       <c r="G40">
         <v>-1.094696830096989</v>
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.5272903394525225</v>
+        <v>-0.5272903394525239</v>
       </c>
       <c r="D41">
-        <v>0.4654711310086966</v>
+        <v>0.4654711310086961</v>
       </c>
       <c r="E41">
         <v>2.548492046230358</v>
       </c>
       <c r="F41">
-        <v>-0.5873309068637075</v>
+        <v>-0.5873309068637097</v>
       </c>
       <c r="G41">
-        <v>-0.6150283100824201</v>
+        <v>-0.6150283100824155</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>2.903222789726887</v>
+        <v>2.90322278972689</v>
       </c>
       <c r="D42">
-        <v>-0.6370926047573744</v>
+        <v>-0.6370926047573731</v>
       </c>
       <c r="E42">
-        <v>-0.7994495607957693</v>
+        <v>-0.7994495607957699</v>
       </c>
       <c r="F42">
-        <v>0.2680177123966885</v>
+        <v>0.2680177123966903</v>
       </c>
       <c r="G42">
-        <v>0.6950959078889399</v>
+        <v>0.6950959078889376</v>
       </c>
     </row>
     <row r="43">
@@ -1513,16 +1513,16 @@
         <v>-1.493554205553412</v>
       </c>
       <c r="D43">
-        <v>-1.426593741389255</v>
+        <v>-1.426593741389257</v>
       </c>
       <c r="E43">
-        <v>1.636114636129223</v>
+        <v>1.636114636129222</v>
       </c>
       <c r="F43">
-        <v>-0.8018380920113309</v>
+        <v>-0.8018380920113358</v>
       </c>
       <c r="G43">
-        <v>-1.238530537756247</v>
+        <v>-1.238530537756243</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.08295083368889546</v>
+        <v>-0.08295083368889461</v>
       </c>
       <c r="D44">
-        <v>-2.608935113672661</v>
+        <v>-2.608935113672662</v>
       </c>
       <c r="E44">
         <v>1.271062720789645</v>
       </c>
       <c r="F44">
-        <v>-3.757802244089646</v>
+        <v>-3.757802244089647</v>
       </c>
       <c r="G44">
-        <v>0.09868044717765292</v>
+        <v>0.0986804471776665</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.5920313062201297</v>
+        <v>0.5920313062201294</v>
       </c>
       <c r="D45">
-        <v>0.2149352652687449</v>
+        <v>0.2149352652687446</v>
       </c>
       <c r="E45">
         <v>1.140608721205443</v>
       </c>
       <c r="F45">
-        <v>-0.3491851082249419</v>
+        <v>-0.3491851082249448</v>
       </c>
       <c r="G45">
-        <v>-0.6076930263128887</v>
+        <v>-0.607693026312887</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-2.480173458843235</v>
+        <v>-2.480173458843234</v>
       </c>
       <c r="D46">
-        <v>-1.519071037261188</v>
+        <v>-1.519071037261191</v>
       </c>
       <c r="E46">
-        <v>-0.9306234767737316</v>
+        <v>-0.9306234767737344</v>
       </c>
       <c r="F46">
-        <v>-0.08384344556322515</v>
+        <v>-0.08384344556322514</v>
       </c>
       <c r="G46">
-        <v>0.1752040104920963</v>
+        <v>0.175204010492098</v>
       </c>
     </row>
     <row r="47">
@@ -1621,16 +1621,16 @@
         <v>2.587441334474506</v>
       </c>
       <c r="D47">
-        <v>1.076040907478346</v>
+        <v>1.076040907478348</v>
       </c>
       <c r="E47">
-        <v>0.07220318886746907</v>
+        <v>0.07220318886746852</v>
       </c>
       <c r="F47">
-        <v>1.466891917704196</v>
+        <v>1.466891917704198</v>
       </c>
       <c r="G47">
-        <v>0.8876693696310901</v>
+        <v>0.8876693696310842</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>3.83563783351892</v>
+        <v>3.835637833518924</v>
       </c>
       <c r="D48">
-        <v>-0.7344246960078731</v>
+        <v>-0.7344246960078704</v>
       </c>
       <c r="E48">
-        <v>-0.6149907052582175</v>
+        <v>-0.6149907052582179</v>
       </c>
       <c r="F48">
-        <v>0.2671971811523361</v>
+        <v>0.2671971811523407</v>
       </c>
       <c r="G48">
-        <v>1.576059074922019</v>
+        <v>1.576059074922017</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.09653691856878448</v>
+        <v>-0.09653691856878488</v>
       </c>
       <c r="D49">
-        <v>0.9462916141053321</v>
+        <v>0.9462916141053307</v>
       </c>
       <c r="E49">
-        <v>1.064207974349253</v>
+        <v>1.064207974349252</v>
       </c>
       <c r="F49">
-        <v>-0.3019661347496527</v>
+        <v>-0.3019661347496588</v>
       </c>
       <c r="G49">
-        <v>-1.415912171917975</v>
+        <v>-1.415912171917973</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.002715005747398151</v>
+        <v>-0.002715005747397553</v>
       </c>
       <c r="D50">
-        <v>-0.7769198469199284</v>
+        <v>-0.7769198469199292</v>
       </c>
       <c r="E50">
-        <v>0.5434731893468427</v>
+        <v>0.5434731893468417</v>
       </c>
       <c r="F50">
-        <v>-0.07779517561473615</v>
+        <v>-0.07779517561473845</v>
       </c>
       <c r="G50">
-        <v>-0.5741574500727017</v>
+        <v>-0.5741574500727007</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.1255887023395502</v>
+        <v>-0.125588702339547</v>
       </c>
       <c r="D51">
-        <v>-3.064958499233618</v>
+        <v>-3.064958499233619</v>
       </c>
       <c r="E51">
-        <v>-0.02815076241938697</v>
+        <v>-0.02815076241938808</v>
       </c>
       <c r="F51">
-        <v>-0.5976816463083201</v>
+        <v>-0.5976816463083223</v>
       </c>
       <c r="G51">
-        <v>-0.6388763291294565</v>
+        <v>-0.638876329129455</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>2.125777835264414</v>
+        <v>2.125777835264417</v>
       </c>
       <c r="D52">
-        <v>-0.9416674219883591</v>
+        <v>-0.941667421988358</v>
       </c>
       <c r="E52">
-        <v>0.3179490564222472</v>
+        <v>0.3179490564222468</v>
       </c>
       <c r="F52">
-        <v>-0.09629699886193774</v>
+        <v>-0.09629699886193718</v>
       </c>
       <c r="G52">
-        <v>0.2814507142224859</v>
+        <v>0.2814507142224854</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>1.359374722984865</v>
+        <v>1.359374722984867</v>
       </c>
       <c r="D53">
-        <v>-0.5184009437548999</v>
+        <v>-0.5184009437548988</v>
       </c>
       <c r="E53">
         <v>1.653485308021829</v>
       </c>
       <c r="F53">
-        <v>1.777944147197804</v>
+        <v>1.777944147197805</v>
       </c>
       <c r="G53">
-        <v>0.109653288773089</v>
+        <v>0.1096532887730846</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.5663990240076305</v>
+        <v>-0.566399024007632</v>
       </c>
       <c r="D54">
-        <v>1.113520239282852</v>
+        <v>1.11352023928285</v>
       </c>
       <c r="E54">
-        <v>0.3605921762152654</v>
+        <v>0.360592176215264</v>
       </c>
       <c r="F54">
-        <v>-0.007781950610548099</v>
+        <v>-0.00778195061055119</v>
       </c>
       <c r="G54">
-        <v>-0.5676096968437436</v>
+        <v>-0.5676096968437425</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.3874599494359321</v>
+        <v>-0.387459949435929</v>
       </c>
       <c r="D55">
-        <v>-0.08068743532755661</v>
+        <v>-0.08068743532755907</v>
       </c>
       <c r="E55">
-        <v>2.066600215090344</v>
+        <v>2.066600215090343</v>
       </c>
       <c r="F55">
-        <v>0.7506692472710539</v>
+        <v>0.7506692472710655</v>
       </c>
       <c r="G55">
-        <v>3.93302459373023</v>
+        <v>3.933024593730223</v>
       </c>
     </row>
     <row r="56">
@@ -1861,16 +1861,16 @@
         </is>
       </c>
       <c r="C56">
-        <v>1.810482405964904</v>
+        <v>1.810482405964905</v>
       </c>
       <c r="D56">
-        <v>-0.5832600432555773</v>
+        <v>-0.5832600432555763</v>
       </c>
       <c r="E56">
-        <v>0.7778592639603682</v>
+        <v>0.777859263960368</v>
       </c>
       <c r="F56">
-        <v>0.1030800628978993</v>
+        <v>0.1030800628979003</v>
       </c>
       <c r="G56">
         <v>0.4894406636476153</v>
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="C57">
-        <v>1.891925110234595</v>
+        <v>1.891925110234598</v>
       </c>
       <c r="D57">
-        <v>-0.9806170050021583</v>
+        <v>-0.9806170050021581</v>
       </c>
       <c r="E57">
-        <v>-1.577065233734024</v>
+        <v>-1.577065233734025</v>
       </c>
       <c r="F57">
-        <v>-0.3437500828724278</v>
+        <v>-0.3437500828724284</v>
       </c>
       <c r="G57">
         <v>0.1561787047092739</v>
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.03071897581346655</v>
+        <v>0.03071897581346719</v>
       </c>
       <c r="D58">
-        <v>-0.4866027314387572</v>
+        <v>-0.4866027314387584</v>
       </c>
       <c r="E58">
-        <v>0.5928371252551912</v>
+        <v>0.5928371252551898</v>
       </c>
       <c r="F58">
-        <v>-1.564271390459846</v>
+        <v>-1.564271390459851</v>
       </c>
       <c r="G58">
-        <v>-1.351278707580063</v>
+        <v>-1.351278707580058</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>2.131834354716871</v>
+        <v>2.131834354716875</v>
       </c>
       <c r="D59">
-        <v>-3.552171653349825</v>
+        <v>-3.552171653349823</v>
       </c>
       <c r="E59">
         <v>1.617566619639654</v>
       </c>
       <c r="F59">
-        <v>-0.4576594809968116</v>
+        <v>-0.45765948099681</v>
       </c>
       <c r="G59">
-        <v>0.3564347166578483</v>
+        <v>0.3564347166578511</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>2.489736463593745</v>
+        <v>2.489736463593748</v>
       </c>
       <c r="D60">
-        <v>-0.8319659161858151</v>
+        <v>-0.8319659161858137</v>
       </c>
       <c r="E60">
-        <v>-0.01795943959016512</v>
+        <v>-0.01795943959016542</v>
       </c>
       <c r="F60">
-        <v>-0.1216007608321228</v>
+        <v>-0.1216007608321208</v>
       </c>
       <c r="G60">
-        <v>0.8778651927286808</v>
+        <v>0.8778651927286809</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.547758960654343</v>
+        <v>-1.547758960654344</v>
       </c>
       <c r="D61">
-        <v>2.007720711823175</v>
+        <v>2.007720711823172</v>
       </c>
       <c r="E61">
-        <v>0.1322189467719555</v>
+        <v>0.1322189467719539</v>
       </c>
       <c r="F61">
-        <v>-0.9294834464825021</v>
+        <v>-0.9294834464825018</v>
       </c>
       <c r="G61">
-        <v>0.5638206108494355</v>
+        <v>0.5638206108494389</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.05032599810408124</v>
+        <v>-0.05032599810408053</v>
       </c>
       <c r="D62">
-        <v>0.2697599961107285</v>
+        <v>0.2697599961107268</v>
       </c>
       <c r="E62">
-        <v>-1.388572589499195</v>
+        <v>-1.388572589499197</v>
       </c>
       <c r="F62">
-        <v>-1.282551821383172</v>
+        <v>-1.282551821383173</v>
       </c>
       <c r="G62">
-        <v>0.2572931042233131</v>
+        <v>0.2572931042233182</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.7463395485979032</v>
+        <v>0.7463395485979035</v>
       </c>
       <c r="D63">
-        <v>1.626861105477902</v>
+        <v>1.626861105477901</v>
       </c>
       <c r="E63">
-        <v>-0.5507385399954691</v>
+        <v>-0.55073853999547</v>
       </c>
       <c r="F63">
-        <v>0.8608196858713767</v>
+        <v>0.8608196858713737</v>
       </c>
       <c r="G63">
-        <v>-0.6541849312033083</v>
+        <v>-0.6541849312033112</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>2.303074017331498</v>
+        <v>2.3030740173315</v>
       </c>
       <c r="D64">
-        <v>-0.2556826737404544</v>
+        <v>-0.2556826737404539</v>
       </c>
       <c r="E64">
-        <v>-1.361806228739505</v>
+        <v>-1.361806228739506</v>
       </c>
       <c r="F64">
-        <v>1.420678587076385</v>
+        <v>1.420678587076384</v>
       </c>
       <c r="G64">
-        <v>-0.04529262503530979</v>
+        <v>-0.04529262503531556</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>3.648631560487241</v>
+        <v>3.648631560487245</v>
       </c>
       <c r="D65">
-        <v>-2.151484794923419</v>
+        <v>-2.151484794923416</v>
       </c>
       <c r="E65">
         <v>-1.351450743369681</v>
       </c>
       <c r="F65">
-        <v>0.5361857415251957</v>
+        <v>0.5361857415251998</v>
       </c>
       <c r="G65">
-        <v>1.194383183648509</v>
+        <v>1.194383183648506</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.2227367028970155</v>
+        <v>0.2227367028970157</v>
       </c>
       <c r="D66">
-        <v>-0.5367882022765258</v>
+        <v>-0.5367882022765263</v>
       </c>
       <c r="E66">
         <v>1.194001773565668</v>
       </c>
       <c r="F66">
-        <v>1.251404453317708</v>
+        <v>1.251404453317703</v>
       </c>
       <c r="G66">
-        <v>-1.047519684673519</v>
+        <v>-1.047519684673522</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>1.382813390309053</v>
+        <v>1.382813390309055</v>
       </c>
       <c r="D67">
-        <v>0.9530011386142211</v>
+        <v>0.953001138614221</v>
       </c>
       <c r="E67">
-        <v>-0.8845832928987333</v>
+        <v>-0.8845832928987344</v>
       </c>
       <c r="F67">
-        <v>-0.7281907492501183</v>
+        <v>-0.7281907492501161</v>
       </c>
       <c r="G67">
-        <v>1.026969558179883</v>
+        <v>1.026969558179885</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.2145500172818346</v>
+        <v>0.2145500172818351</v>
       </c>
       <c r="D68">
-        <v>1.744822665321945</v>
+        <v>1.744822665321943</v>
       </c>
       <c r="E68">
-        <v>-1.159134521768909</v>
+        <v>-1.15913452176891</v>
       </c>
       <c r="F68">
-        <v>-0.2160950225857992</v>
+        <v>-0.2160950225858022</v>
       </c>
       <c r="G68">
-        <v>-0.4769748147879261</v>
+        <v>-0.476974814787925</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.9613107032587803</v>
+        <v>0.9613107032587818</v>
       </c>
       <c r="D69">
-        <v>-0.2653450630496731</v>
+        <v>-0.265345063049673</v>
       </c>
       <c r="E69">
-        <v>-0.2266705093455165</v>
+        <v>-0.2266705093455169</v>
       </c>
       <c r="F69">
-        <v>0.7176542644476088</v>
+        <v>0.7176542644476077</v>
       </c>
       <c r="G69">
-        <v>-0.3147631266349304</v>
+        <v>-0.3147631266349329</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>1.956902064574928</v>
+        <v>1.95690206457493</v>
       </c>
       <c r="D70">
-        <v>-0.4853307818422673</v>
+        <v>-0.4853307818422667</v>
       </c>
       <c r="E70">
-        <v>-0.4377998834409972</v>
+        <v>-0.4377998834409981</v>
       </c>
       <c r="F70">
-        <v>-0.6686977263366166</v>
+        <v>-0.6686977263366144</v>
       </c>
       <c r="G70">
-        <v>0.7939297700689291</v>
+        <v>0.7939297700689303</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.1965655957400325</v>
+        <v>-0.1965655957400324</v>
       </c>
       <c r="D71">
-        <v>1.913398319609907</v>
+        <v>1.913398319609906</v>
       </c>
       <c r="E71">
-        <v>-0.1107084441104476</v>
+        <v>-0.1107084441104491</v>
       </c>
       <c r="F71">
-        <v>0.4033498225254885</v>
+        <v>0.4033498225254863</v>
       </c>
       <c r="G71">
-        <v>-0.3787390113056248</v>
+        <v>-0.3787390113056249</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-4.356356562663266</v>
+        <v>-4.356356562663269</v>
       </c>
       <c r="D72">
-        <v>2.428582058475995</v>
+        <v>2.428582058475992</v>
       </c>
       <c r="E72">
-        <v>0.1613401718198617</v>
+        <v>0.1613401718198585</v>
       </c>
       <c r="F72">
-        <v>3.599612891481093</v>
+        <v>3.599612891481097</v>
       </c>
       <c r="G72">
-        <v>1.27018238632009</v>
+        <v>1.27018238632008</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-7.71860438381508</v>
+        <v>-7.718604383815078</v>
       </c>
       <c r="D73">
-        <v>-4.930601202308583</v>
+        <v>-4.93060120230859</v>
       </c>
       <c r="E73">
-        <v>-1.016625969171744</v>
+        <v>-1.016625969171751</v>
       </c>
       <c r="F73">
-        <v>2.666588589676986</v>
+        <v>2.666588589676996</v>
       </c>
       <c r="G73">
-        <v>2.858118090083311</v>
+        <v>2.858118090083305</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.2072833177488513</v>
+        <v>0.2072833177488491</v>
       </c>
       <c r="D74">
         <v>1.232672720856785</v>
       </c>
       <c r="E74">
-        <v>2.146507618261828</v>
+        <v>2.146507618261829</v>
       </c>
       <c r="F74">
-        <v>0.8027032954385107</v>
+        <v>0.8027032954385083</v>
       </c>
       <c r="G74">
-        <v>-0.07972162760208071</v>
+        <v>-0.07972162760208107</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-2.916727768455744</v>
+        <v>-2.916727768455741</v>
       </c>
       <c r="D75">
-        <v>-3.116414089795811</v>
+        <v>-3.116414089795814</v>
       </c>
       <c r="E75">
-        <v>-2.421847999220777</v>
+        <v>-2.421847999220778</v>
       </c>
       <c r="F75">
-        <v>-0.1977854321418492</v>
+        <v>-0.1977854321418537</v>
       </c>
       <c r="G75">
-        <v>-1.100485963410289</v>
+        <v>-1.100485963410287</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-3.499167012772826</v>
+        <v>-3.499167012772824</v>
       </c>
       <c r="D76">
-        <v>-1.251590681657593</v>
+        <v>-1.251590681657597</v>
       </c>
       <c r="E76">
-        <v>-0.7015830678172364</v>
+        <v>-0.7015830678172399</v>
       </c>
       <c r="F76">
-        <v>0.6974117447357466</v>
+        <v>0.6974117447357491</v>
       </c>
       <c r="G76">
-        <v>0.7780113942783791</v>
+        <v>0.778011394278378</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.1624392106286634</v>
+        <v>0.1624392106286633</v>
       </c>
       <c r="D77">
         <v>1.768262722603912</v>
       </c>
       <c r="E77">
-        <v>-0.1977504257907902</v>
+        <v>-0.1977504257907908</v>
       </c>
       <c r="F77">
-        <v>-0.04603822410625438</v>
+        <v>-0.04603822410625486</v>
       </c>
       <c r="G77">
-        <v>0.1065050716547506</v>
+        <v>0.106505071654752</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.8217984250835085</v>
+        <v>0.82179842508351</v>
       </c>
       <c r="D78">
-        <v>0.07097086043683662</v>
+        <v>0.07097086043683611</v>
       </c>
       <c r="E78">
-        <v>-1.20173311176731</v>
+        <v>-1.201733111767312</v>
       </c>
       <c r="F78">
-        <v>-0.2382401567685151</v>
+        <v>-0.2382401567685146</v>
       </c>
       <c r="G78">
-        <v>0.161503491698492</v>
+        <v>0.161503491698493</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.4920766053336222</v>
+        <v>-0.4920766053336235</v>
       </c>
       <c r="D79">
-        <v>1.267012245098335</v>
+        <v>1.267012245098334</v>
       </c>
       <c r="E79">
-        <v>0.7978347222554009</v>
+        <v>0.7978347222553993</v>
       </c>
       <c r="F79">
-        <v>-1.6999063208459</v>
+        <v>-1.699906320845899</v>
       </c>
       <c r="G79">
-        <v>0.5539457833098321</v>
+        <v>0.5539457833098396</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.1596586245528221</v>
+        <v>-0.1596586245528225</v>
       </c>
       <c r="D80">
-        <v>1.509501863756176</v>
+        <v>1.509501863756175</v>
       </c>
       <c r="E80">
-        <v>0.9795820324581845</v>
+        <v>0.9795820324581831</v>
       </c>
       <c r="F80">
-        <v>0.0608926972742779</v>
+        <v>0.06089269727427633</v>
       </c>
       <c r="G80">
-        <v>-0.3627729962812418</v>
+        <v>-0.3627729962812405</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.01622939440955889</v>
+        <v>-0.01622939440955766</v>
       </c>
       <c r="D81">
-        <v>0.8898184822216848</v>
+        <v>0.8898184822216836</v>
       </c>
       <c r="E81">
-        <v>-1.12794285823319</v>
+        <v>-1.127942858233192</v>
       </c>
       <c r="F81">
-        <v>1.103258510701186</v>
+        <v>1.103258510701185</v>
       </c>
       <c r="G81">
-        <v>-0.06065555302388715</v>
+        <v>-0.06065555302388964</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.7486001298139804</v>
+        <v>0.7486001298139825</v>
       </c>
       <c r="D82">
         <v>-0.6537560069908108</v>
       </c>
       <c r="E82">
-        <v>0.6514011077199067</v>
+        <v>0.6514011077199057</v>
       </c>
       <c r="F82">
-        <v>-0.1102690668159503</v>
+        <v>-0.1102690668159531</v>
       </c>
       <c r="G82">
-        <v>-0.8512755903325804</v>
+        <v>-0.8512755903325802</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.174254770754242</v>
+        <v>-0.1742547707542405</v>
       </c>
       <c r="D83">
         <v>-2.548192601395607</v>
       </c>
       <c r="E83">
-        <v>0.6490544614373323</v>
+        <v>0.6490544614373318</v>
       </c>
       <c r="F83">
-        <v>-0.4870216820625793</v>
+        <v>-0.4870216820625809</v>
       </c>
       <c r="G83">
-        <v>-0.4565597018797984</v>
+        <v>-0.4565597018797958</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-2.043375171374395</v>
+        <v>-2.043375171374394</v>
       </c>
       <c r="D84">
-        <v>-0.3853545853382594</v>
+        <v>-0.3853545853382637</v>
       </c>
       <c r="E84">
-        <v>-1.640250870256682</v>
+        <v>-1.640250870256684</v>
       </c>
       <c r="F84">
-        <v>-1.299450108370562</v>
+        <v>-1.299450108370559</v>
       </c>
       <c r="G84">
-        <v>1.115429624346497</v>
+        <v>1.115429624346499</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>2.701819707689723</v>
+        <v>2.701819707689727</v>
       </c>
       <c r="D85">
-        <v>-1.019122523316896</v>
+        <v>-1.019122523316895</v>
       </c>
       <c r="E85">
-        <v>-1.726731464038806</v>
+        <v>-1.726731464038807</v>
       </c>
       <c r="F85">
-        <v>0.423666888706036</v>
+        <v>0.4236668887060378</v>
       </c>
       <c r="G85">
-        <v>0.5694821790352889</v>
+        <v>0.5694821790352862</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.660840234718085</v>
+        <v>2.660840234718088</v>
       </c>
       <c r="D86">
-        <v>-2.08537481589396</v>
+        <v>-2.085374815893958</v>
       </c>
       <c r="E86">
-        <v>0.3152280308312178</v>
+        <v>0.3152280308312177</v>
       </c>
       <c r="F86">
-        <v>0.3490286675636098</v>
+        <v>0.349028667563612</v>
       </c>
       <c r="G86">
-        <v>0.7457955201523228</v>
+        <v>0.7457955201523205</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.5876809192514294</v>
+        <v>-0.5876809192514295</v>
       </c>
       <c r="D87">
-        <v>1.323212867680875</v>
+        <v>1.323212867680873</v>
       </c>
       <c r="E87">
-        <v>-0.5091884924767784</v>
+        <v>-0.5091884924767798</v>
       </c>
       <c r="F87">
-        <v>-0.04607227438443464</v>
+        <v>-0.04607227438443697</v>
       </c>
       <c r="G87">
-        <v>-0.3631573908886407</v>
+        <v>-0.3631573908886393</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>3.710607312888587</v>
+        <v>3.710607312888591</v>
       </c>
       <c r="D88">
-        <v>-0.7246762243819599</v>
+        <v>-0.7246762243819574</v>
       </c>
       <c r="E88">
-        <v>-1.613156874095791</v>
+        <v>-1.613156874095792</v>
       </c>
       <c r="F88">
-        <v>-0.4582232954369838</v>
+        <v>-0.4582232954369789</v>
       </c>
       <c r="G88">
-        <v>1.717179578505472</v>
+        <v>1.717179578505471</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.8351006702161021</v>
+        <v>-0.8351006702161037</v>
       </c>
       <c r="D89">
-        <v>0.3549382089009674</v>
+        <v>0.3549382089009669</v>
       </c>
       <c r="E89">
-        <v>2.252900985898541</v>
+        <v>2.25290098589854</v>
       </c>
       <c r="F89">
-        <v>-1.298435217708464</v>
+        <v>-1.298435217708467</v>
       </c>
       <c r="G89">
-        <v>-0.8368865780758764</v>
+        <v>-0.8368865780758705</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.5710840481119938</v>
+        <v>-0.5710840481119954</v>
       </c>
       <c r="D90">
-        <v>2.066951096654793</v>
+        <v>2.066951096654791</v>
       </c>
       <c r="E90">
-        <v>-0.07257693485171259</v>
+        <v>-0.07257693485171357</v>
       </c>
       <c r="F90">
-        <v>-0.09300113559815712</v>
+        <v>-0.09300113559816051</v>
       </c>
       <c r="G90">
-        <v>-0.7708212781156302</v>
+        <v>-0.7708212781156289</v>
       </c>
     </row>
     <row r="91">
@@ -2809,13 +2809,13 @@
         <v>-0.1246047183253094</v>
       </c>
       <c r="D91">
-        <v>0.9645777909981537</v>
+        <v>0.9645777909981517</v>
       </c>
       <c r="E91">
-        <v>-1.162979837308435</v>
+        <v>-1.162979837308436</v>
       </c>
       <c r="F91">
-        <v>-0.07068594650475821</v>
+        <v>-0.07068594650476319</v>
       </c>
       <c r="G91">
         <v>-1.269370443480498</v>
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.05469696248486709</v>
+        <v>0.05469696248486669</v>
       </c>
       <c r="D92">
-        <v>-0.7606039366499741</v>
+        <v>-0.7606039366499743</v>
       </c>
       <c r="E92">
-        <v>1.577493456081539</v>
+        <v>1.57749345608154</v>
       </c>
       <c r="F92">
-        <v>0.5344593171895076</v>
+        <v>0.5344593171895046</v>
       </c>
       <c r="G92">
-        <v>-0.692531199423692</v>
+        <v>-0.6925311994236929</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.7917602619681636</v>
+        <v>0.7917602619681644</v>
       </c>
       <c r="D93">
-        <v>0.5886314153410389</v>
+        <v>0.5886314153410388</v>
       </c>
       <c r="E93">
-        <v>0.07592619622261763</v>
+        <v>0.07592619622261687</v>
       </c>
       <c r="F93">
-        <v>-0.05404705637727008</v>
+        <v>-0.0540470563772707</v>
       </c>
       <c r="G93">
-        <v>-0.1499856208084896</v>
+        <v>-0.1499856208084887</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-1.070301975371743</v>
+        <v>-1.070301975371745</v>
       </c>
       <c r="D94">
-        <v>3.619332824957268</v>
+        <v>3.619332824957266</v>
       </c>
       <c r="E94">
-        <v>0.1955205966614191</v>
+        <v>0.1955205966614184</v>
       </c>
       <c r="F94">
-        <v>0.7466327381549671</v>
+        <v>0.7466327381549634</v>
       </c>
       <c r="G94">
-        <v>-0.5212815897725976</v>
+        <v>-0.5212815897725979</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-3.418664989026674</v>
+        <v>-3.418664989026673</v>
       </c>
       <c r="D95">
-        <v>-3.497789422533775</v>
+        <v>-3.497789422533778</v>
       </c>
       <c r="E95">
-        <v>-0.3398793453520403</v>
+        <v>-0.3398793453520426</v>
       </c>
       <c r="F95">
-        <v>1.156909096577568</v>
+        <v>1.156909096577565</v>
       </c>
       <c r="G95">
-        <v>-0.619622405995981</v>
+        <v>-0.6196224059959825</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.4276175345208252</v>
+        <v>-0.4276175345208242</v>
       </c>
       <c r="D96">
-        <v>-0.3958081600707251</v>
+        <v>-0.3958081600707267</v>
       </c>
       <c r="E96">
-        <v>-0.3321538547207523</v>
+        <v>-0.332153854720753</v>
       </c>
       <c r="F96">
-        <v>0.02369071709927648</v>
+        <v>0.02369071709927249</v>
       </c>
       <c r="G96">
-        <v>-0.8418003131667816</v>
+        <v>-0.8418003131667815</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>1.645160795385246</v>
+        <v>1.645160795385248</v>
       </c>
       <c r="D97">
-        <v>-0.7363395826578568</v>
+        <v>-0.7363395826578573</v>
       </c>
       <c r="E97">
-        <v>-2.399822638490589</v>
+        <v>-2.39982263849059</v>
       </c>
       <c r="F97">
-        <v>-0.4929708752655474</v>
+        <v>-0.4929708752655481</v>
       </c>
       <c r="G97">
-        <v>0.08117245808525361</v>
+        <v>0.08117245808525364</v>
       </c>
     </row>
     <row r="98">
@@ -2998,16 +2998,16 @@
         <v>-1.832261377962032</v>
       </c>
       <c r="D98">
-        <v>-1.051864202755756</v>
+        <v>-1.051864202755759</v>
       </c>
       <c r="E98">
-        <v>-1.724097531157226</v>
+        <v>-1.724097531157228</v>
       </c>
       <c r="F98">
-        <v>-0.04953879074951579</v>
+        <v>-0.04953879074951772</v>
       </c>
       <c r="G98">
-        <v>-0.574605326495229</v>
+        <v>-0.5746053264952274</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.930100276628199</v>
+        <v>1.930100276628201</v>
       </c>
       <c r="D99">
-        <v>0.008555949151666983</v>
+        <v>0.008555949151668449</v>
       </c>
       <c r="E99">
-        <v>0.411751745956912</v>
+        <v>0.4117517459569114</v>
       </c>
       <c r="F99">
-        <v>1.562072615884625</v>
+        <v>1.562072615884629</v>
       </c>
       <c r="G99">
-        <v>1.476323275532974</v>
+        <v>1.47632327553297</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.1872762887020452</v>
+        <v>-0.187276288702045</v>
       </c>
       <c r="D100">
-        <v>0.9542782588886775</v>
+        <v>0.9542782588886756</v>
       </c>
       <c r="E100">
-        <v>-1.107114141316419</v>
+        <v>-1.10711414131642</v>
       </c>
       <c r="F100">
-        <v>-1.446160349885027</v>
+        <v>-1.446160349885028</v>
       </c>
       <c r="G100">
-        <v>0.00923717567104373</v>
+        <v>0.009237175671049203</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.3629987833044837</v>
+        <v>0.3629987833044832</v>
       </c>
       <c r="D101">
-        <v>1.282188850755242</v>
+        <v>1.282188850755241</v>
       </c>
       <c r="E101">
-        <v>0.7477615929849811</v>
+        <v>0.74776159298498</v>
       </c>
       <c r="F101">
-        <v>-0.1401451196839153</v>
+        <v>-0.1401451196839163</v>
       </c>
       <c r="G101">
-        <v>-0.1305422654294563</v>
+        <v>-0.130542265429455</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.6804496115905423</v>
+        <v>0.6804496115905426</v>
       </c>
       <c r="D102">
-        <v>0.3368466682233784</v>
+        <v>0.3368466682233791</v>
       </c>
       <c r="E102">
         <v>1.272965869888173</v>
       </c>
       <c r="F102">
-        <v>0.8838937559258614</v>
+        <v>0.8838937559258615</v>
       </c>
       <c r="G102">
-        <v>0.08304711639833603</v>
+        <v>0.08304711639833484</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>1.132423769824053</v>
+        <v>1.132423769824054</v>
       </c>
       <c r="D103">
-        <v>-0.6150047325801661</v>
+        <v>-0.6150047325801672</v>
       </c>
       <c r="E103">
-        <v>-0.8837532785991087</v>
+        <v>-0.8837532785991097</v>
       </c>
       <c r="F103">
-        <v>-1.241370947156763</v>
+        <v>-1.241370947156764</v>
       </c>
       <c r="G103">
-        <v>0.1662520414646099</v>
+        <v>0.1662520414646139</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>1.64452370296853</v>
+        <v>1.644523702968532</v>
       </c>
       <c r="D104">
-        <v>0.5681456873498917</v>
+        <v>0.5681456873498911</v>
       </c>
       <c r="E104">
-        <v>-2.648598614004395</v>
+        <v>-2.648598614004396</v>
       </c>
       <c r="F104">
-        <v>-0.8115316553903671</v>
+        <v>-0.8115316553903672</v>
       </c>
       <c r="G104">
-        <v>0.09231182555388481</v>
+        <v>0.09231182555388634</v>
       </c>
     </row>
     <row r="105">
@@ -3187,16 +3187,16 @@
         <v>1.074642807562157</v>
       </c>
       <c r="D105">
-        <v>0.499526044488309</v>
+        <v>0.4995260444883087</v>
       </c>
       <c r="E105">
-        <v>-0.8665513271984824</v>
+        <v>-0.8665513271984839</v>
       </c>
       <c r="F105">
-        <v>-0.9625802735277987</v>
+        <v>-0.9625802735277982</v>
       </c>
       <c r="G105">
-        <v>0.3647422673228759</v>
+        <v>0.3647422673228788</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-2.208612861262734</v>
+        <v>-2.208612861262733</v>
       </c>
       <c r="D106">
-        <v>0.01734915779672389</v>
+        <v>0.01734915779672039</v>
       </c>
       <c r="E106">
-        <v>-0.1159766192168891</v>
+        <v>-0.1159766192168915</v>
       </c>
       <c r="F106">
-        <v>-0.4065383303726405</v>
+        <v>-0.4065383303726395</v>
       </c>
       <c r="G106">
-        <v>0.5124102236247405</v>
+        <v>0.5124102236247412</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.3899569824668401</v>
+        <v>0.3899569824668406</v>
       </c>
       <c r="D107">
-        <v>0.6584555926158904</v>
+        <v>0.6584555926158898</v>
       </c>
       <c r="E107">
-        <v>0.01705604091644545</v>
+        <v>0.0170560409164442</v>
       </c>
       <c r="F107">
-        <v>-0.3947867408263687</v>
+        <v>-0.3947867408263688</v>
       </c>
       <c r="G107">
-        <v>0.1697906910331768</v>
+        <v>0.1697906910331791</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.4234646542086389</v>
+        <v>0.4234646542086403</v>
       </c>
       <c r="D108">
-        <v>0.1127816933326878</v>
+        <v>0.1127816933326863</v>
       </c>
       <c r="E108">
-        <v>-1.840683640569891</v>
+        <v>-1.840683640569892</v>
       </c>
       <c r="F108">
-        <v>-0.4019813920106309</v>
+        <v>-0.401981392010633</v>
       </c>
       <c r="G108">
-        <v>-0.613842421707026</v>
+        <v>-0.6138424217070251</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>1.179248584021266</v>
+        <v>1.179248584021267</v>
       </c>
       <c r="D109">
-        <v>0.64464676809751</v>
+        <v>0.6446467680975099</v>
       </c>
       <c r="E109">
-        <v>-0.6627749869384736</v>
+        <v>-0.6627749869384744</v>
       </c>
       <c r="F109">
-        <v>1.000068465876891</v>
+        <v>1.000068465876889</v>
       </c>
       <c r="G109">
-        <v>-0.701488492766852</v>
+        <v>-0.7014884927668557</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-1.497844692880548</v>
+        <v>-1.497844692880546</v>
       </c>
       <c r="D110">
-        <v>-1.741409930408129</v>
+        <v>-1.741409930408131</v>
       </c>
       <c r="E110">
-        <v>0.9395918848526041</v>
+        <v>0.9395918848526024</v>
       </c>
       <c r="F110">
-        <v>0.1993933661656214</v>
+        <v>0.1993933661656235</v>
       </c>
       <c r="G110">
-        <v>0.6855542411499272</v>
+        <v>0.6855542411499267</v>
       </c>
     </row>
     <row r="111">
@@ -3349,16 +3349,16 @@
         <v>1.243856572947172</v>
       </c>
       <c r="D111">
-        <v>0.6285176514966953</v>
+        <v>0.6285176514966959</v>
       </c>
       <c r="E111">
         <v>1.788358616151744</v>
       </c>
       <c r="F111">
-        <v>1.639524170703661</v>
+        <v>1.639524170703658</v>
       </c>
       <c r="G111">
-        <v>-0.1531200438461687</v>
+        <v>-0.1531200438461732</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.2767921259678141</v>
+        <v>0.2767921259678151</v>
       </c>
       <c r="D112">
-        <v>-2.165743352758867</v>
+        <v>-2.165743352758865</v>
       </c>
       <c r="E112">
-        <v>3.249109740268691</v>
+        <v>3.249109740268692</v>
       </c>
       <c r="F112">
-        <v>0.3061817999681489</v>
+        <v>0.3061817999681476</v>
       </c>
       <c r="G112">
-        <v>-0.9377050188427107</v>
+        <v>-0.9377050188427103</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>0.9909510036636536</v>
+        <v>0.990951003663656</v>
       </c>
       <c r="D113">
-        <v>1.190257815226944</v>
+        <v>1.190257815226943</v>
       </c>
       <c r="E113">
-        <v>-1.744636834152961</v>
+        <v>-1.744636834152962</v>
       </c>
       <c r="F113">
-        <v>0.06687820881273945</v>
+        <v>0.06687820881273975</v>
       </c>
       <c r="G113">
-        <v>0.1983964965813695</v>
+        <v>0.1983964965813689</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.970945189719294</v>
+        <v>-0.9709451897192906</v>
       </c>
       <c r="D114">
-        <v>-2.152466353163683</v>
+        <v>-2.152466353163687</v>
       </c>
       <c r="E114">
-        <v>-3.195919810414639</v>
+        <v>-3.195919810414642</v>
       </c>
       <c r="F114">
-        <v>1.434040046430806</v>
+        <v>1.434040046430801</v>
       </c>
       <c r="G114">
-        <v>-1.58617707343058</v>
+        <v>-1.586177073430586</v>
       </c>
     </row>
     <row r="115">
@@ -3457,16 +3457,16 @@
         <v>-2.487430439008234</v>
       </c>
       <c r="D115">
-        <v>-2.886128952316264</v>
+        <v>-2.886128952316267</v>
       </c>
       <c r="E115">
         <v>3.085246496578513</v>
       </c>
       <c r="F115">
-        <v>-3.051003599846899</v>
+        <v>-3.051003599846906</v>
       </c>
       <c r="G115">
-        <v>-1.453995498728424</v>
+        <v>-1.45399549872841</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.655089130246828</v>
+        <v>-1.655089130246827</v>
       </c>
       <c r="D116">
-        <v>-0.9388275718153113</v>
+        <v>-0.9388275718153141</v>
       </c>
       <c r="E116">
-        <v>0.3092276121503688</v>
+        <v>0.3092276121503665</v>
       </c>
       <c r="F116">
-        <v>-1.28364671653829</v>
+        <v>-1.283646716538289</v>
       </c>
       <c r="G116">
-        <v>0.6580409740092055</v>
+        <v>0.6580409740092108</v>
       </c>
     </row>
     <row r="117">
@@ -3511,16 +3511,16 @@
         <v>-1.725542344911338</v>
       </c>
       <c r="D117">
-        <v>1.549008941808707</v>
+        <v>1.549008941808705</v>
       </c>
       <c r="E117">
-        <v>-0.005462128393739403</v>
+        <v>-0.005462128393742105</v>
       </c>
       <c r="F117">
-        <v>1.015887490868084</v>
+        <v>1.015887490868089</v>
       </c>
       <c r="G117">
-        <v>1.415369393883476</v>
+        <v>1.415369393883473</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>1.928086612772545</v>
+        <v>1.928086612772548</v>
       </c>
       <c r="D118">
-        <v>-0.6654110962111686</v>
+        <v>-0.6654110962111668</v>
       </c>
       <c r="E118">
-        <v>1.299963719080641</v>
+        <v>1.29996371908064</v>
       </c>
       <c r="F118">
-        <v>1.794586492752019</v>
+        <v>1.794586492752021</v>
       </c>
       <c r="G118">
-        <v>0.7970324909446932</v>
+        <v>0.7970324909446884</v>
       </c>
     </row>
     <row r="119">
@@ -3565,16 +3565,16 @@
         <v>-1.719780368534306</v>
       </c>
       <c r="D119">
-        <v>0.5679831591777782</v>
+        <v>0.5679831591777741</v>
       </c>
       <c r="E119">
-        <v>-2.157441538232902</v>
+        <v>-2.157441538232904</v>
       </c>
       <c r="F119">
-        <v>-1.10394198590511</v>
+        <v>-1.103941985905112</v>
       </c>
       <c r="G119">
-        <v>-0.3270627994395034</v>
+        <v>-0.3270627994395012</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.4567424611392584</v>
+        <v>0.45674246113926</v>
       </c>
       <c r="D120">
         <v>-0.1394254001708664</v>
       </c>
       <c r="E120">
-        <v>0.5727958350397683</v>
+        <v>0.5727958350397676</v>
       </c>
       <c r="F120">
-        <v>1.716753300619415</v>
+        <v>1.71675330061941</v>
       </c>
       <c r="G120">
-        <v>-1.504920748429652</v>
+        <v>-1.504920748429658</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.1405871102720531</v>
+        <v>-0.1405871102720522</v>
       </c>
       <c r="D121">
-        <v>0.839152541351723</v>
+        <v>0.8391525413517219</v>
       </c>
       <c r="E121">
-        <v>-0.6517082331721447</v>
+        <v>-0.6517082331721459</v>
       </c>
       <c r="F121">
-        <v>1.519800735245372</v>
+        <v>1.51980073524537</v>
       </c>
       <c r="G121">
-        <v>-0.7041544289876989</v>
+        <v>-0.7041544289877024</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-1.214672089520726</v>
+        <v>-1.214672089520727</v>
       </c>
       <c r="D122">
-        <v>0.4045411371041394</v>
+        <v>0.4045411371041382</v>
       </c>
       <c r="E122">
         <v>2.110688029323779</v>
       </c>
       <c r="F122">
-        <v>-0.1638628488506517</v>
+        <v>-0.1638628488506555</v>
       </c>
       <c r="G122">
-        <v>-0.9545968697300483</v>
+        <v>-0.9545968697300451</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.9631855471952248</v>
+        <v>0.9631855471952256</v>
       </c>
       <c r="D123">
-        <v>0.7735006734832739</v>
+        <v>0.7735006734832731</v>
       </c>
       <c r="E123">
         <v>-1.377209995357213</v>
       </c>
       <c r="F123">
-        <v>0.6191597901670938</v>
+        <v>0.619159790167094</v>
       </c>
       <c r="G123">
-        <v>0.3270015219536746</v>
+        <v>0.3270015219536707</v>
       </c>
     </row>
     <row r="124">
@@ -3700,16 +3700,16 @@
         <v>-1.367333706667223</v>
       </c>
       <c r="D124">
-        <v>0.6062073676045482</v>
+        <v>0.6062073676045455</v>
       </c>
       <c r="E124">
-        <v>0.1944213113577813</v>
+        <v>0.19442131135778</v>
       </c>
       <c r="F124">
-        <v>-0.07313116850184763</v>
+        <v>-0.07313116850185172</v>
       </c>
       <c r="G124">
-        <v>-0.9428882420218877</v>
+        <v>-0.9428882420218879</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.8546209191122827</v>
+        <v>-0.8546209191122812</v>
       </c>
       <c r="D125">
-        <v>-0.3919732948977376</v>
+        <v>-0.3919732948977389</v>
       </c>
       <c r="E125">
-        <v>0.5057713420837502</v>
+        <v>0.5057713420837492</v>
       </c>
       <c r="F125">
-        <v>0.9455774211955981</v>
+        <v>0.9455774211955992</v>
       </c>
       <c r="G125">
-        <v>0.594063970462947</v>
+        <v>0.5940639704629456</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-2.656786934020022</v>
+        <v>-2.656786934020019</v>
       </c>
       <c r="D126">
-        <v>-1.519811175834572</v>
+        <v>-1.519811175834576</v>
       </c>
       <c r="E126">
-        <v>-2.153479509300794</v>
+        <v>-2.153479509300798</v>
       </c>
       <c r="F126">
-        <v>0.5110718999119988</v>
+        <v>0.5110718999120015</v>
       </c>
       <c r="G126">
-        <v>0.8605014104949286</v>
+        <v>0.8605014104949255</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/all/03_DS/ds_idx10_juventud.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx10_juventud.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.058249087988643</v>
+        <v>3.42284431543177</v>
       </c>
       <c r="D2">
-        <v>-1.145109845431552</v>
+        <v>-1.533496411400556</v>
       </c>
       <c r="E2">
-        <v>-0.4288595452115398</v>
+        <v>-0.892421773181873</v>
       </c>
       <c r="F2">
-        <v>-0.3960634271100602</v>
+        <v>-0.9097235331120618</v>
       </c>
       <c r="G2">
-        <v>0.5136184984558807</v>
+        <v>1.507314925508106</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.5068052052360665</v>
+        <v>-0.7717797708657451</v>
       </c>
       <c r="D3">
-        <v>1.233262103925824</v>
+        <v>1.186552916365934</v>
       </c>
       <c r="E3">
-        <v>0.6099211008706608</v>
+        <v>0.5318995677608463</v>
       </c>
       <c r="F3">
-        <v>-0.1464040629102908</v>
+        <v>-0.07896075099881338</v>
       </c>
       <c r="G3">
-        <v>-0.4953117318819929</v>
+        <v>-0.3594430567463361</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4253190302663208</v>
+        <v>-0.1403541775755958</v>
       </c>
       <c r="D4">
-        <v>3.00744586847724</v>
+        <v>3.098240538559619</v>
       </c>
       <c r="E4">
-        <v>1.403944349525694</v>
+        <v>1.21722355064949</v>
       </c>
       <c r="F4">
-        <v>-0.3349251825504388</v>
+        <v>-0.4282510181520727</v>
       </c>
       <c r="G4">
-        <v>0.09842897848026916</v>
+        <v>0.2124974449650371</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.585382632169328</v>
+        <v>0.228400519118905</v>
       </c>
       <c r="D5">
-        <v>1.779718760704279</v>
+        <v>1.874593011276473</v>
       </c>
       <c r="E5">
-        <v>-0.8116316221226437</v>
+        <v>-0.8185357761798473</v>
       </c>
       <c r="F5">
-        <v>-1.056767516931022</v>
+        <v>-0.79052969731117</v>
       </c>
       <c r="G5">
-        <v>-0.8655267720879434</v>
+        <v>-1.15546881470155</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.8414813909967314</v>
+        <v>0.6806476334092064</v>
       </c>
       <c r="D6">
-        <v>-0.2902292231515735</v>
+        <v>-0.0009781325340130296</v>
       </c>
       <c r="E6">
-        <v>0.9075160685869437</v>
+        <v>1.068873274982947</v>
       </c>
       <c r="F6">
-        <v>0.7996414897689496</v>
+        <v>1.043723594594904</v>
       </c>
       <c r="G6">
-        <v>-0.9893101061251013</v>
+        <v>-0.8322833185649728</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3617624276915842</v>
+        <v>-0.6363313031490199</v>
       </c>
       <c r="D7">
-        <v>1.620643623449947</v>
+        <v>1.547538651270073</v>
       </c>
       <c r="E7">
-        <v>0.6071197162182528</v>
+        <v>0.4443717452497976</v>
       </c>
       <c r="F7">
-        <v>0.1216380661047786</v>
+        <v>-0.1344472182589013</v>
       </c>
       <c r="G7">
-        <v>0.7743877549468825</v>
+        <v>0.9468755366596031</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.8624132329466511</v>
+        <v>0.921045171193385</v>
       </c>
       <c r="D8">
-        <v>-0.465799874067906</v>
+        <v>-0.3022212679529683</v>
       </c>
       <c r="E8">
-        <v>0.6327464860405835</v>
+        <v>0.6779612387917573</v>
       </c>
       <c r="F8">
-        <v>0.164733102738788</v>
+        <v>0.1044593593218454</v>
       </c>
       <c r="G8">
-        <v>0.2247995565871126</v>
+        <v>0.2581916420824911</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.7789745909031167</v>
+        <v>0.6309371552400868</v>
       </c>
       <c r="D9">
-        <v>0.188917271179123</v>
+        <v>0.3622346986060679</v>
       </c>
       <c r="E9">
-        <v>-1.471454806526667</v>
+        <v>-1.303881359734717</v>
       </c>
       <c r="F9">
-        <v>-0.02652557400423824</v>
+        <v>0.3472755466398721</v>
       </c>
       <c r="G9">
-        <v>-1.037015789269914</v>
+        <v>-1.33105687573681</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-1.294546914989528</v>
+        <v>-1.671083209979987</v>
       </c>
       <c r="D10">
-        <v>2.483826555023258</v>
+        <v>2.227547670481409</v>
       </c>
       <c r="E10">
-        <v>0.07146957871475745</v>
+        <v>-0.1462104219181613</v>
       </c>
       <c r="F10">
-        <v>-0.8976782121991224</v>
+        <v>-0.7951770301505205</v>
       </c>
       <c r="G10">
-        <v>-0.8020781549380969</v>
+        <v>-0.6661761197874133</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-2.74233717358236</v>
+        <v>-2.933906360080433</v>
       </c>
       <c r="D11">
-        <v>1.863985693281235</v>
+        <v>1.338524895872511</v>
       </c>
       <c r="E11">
-        <v>1.240164242497325</v>
+        <v>0.835342904325045</v>
       </c>
       <c r="F11">
-        <v>-2.020892827299455</v>
+        <v>-2.648666702213545</v>
       </c>
       <c r="G11">
-        <v>2.373844224158865</v>
+        <v>2.076913909699694</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.1842835290951261</v>
+        <v>0.7334067726389021</v>
       </c>
       <c r="D12">
-        <v>-0.5269721099026301</v>
+        <v>-0.7681558693526773</v>
       </c>
       <c r="E12">
-        <v>-0.2346104841867937</v>
+        <v>-0.4002220337092263</v>
       </c>
       <c r="F12">
-        <v>0.833651325108142</v>
+        <v>0.7933916774438361</v>
       </c>
       <c r="G12">
-        <v>-0.6352297699373944</v>
+        <v>0.05872973812425888</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-1.265555569106477</v>
+        <v>-1.467201579127649</v>
       </c>
       <c r="D13">
-        <v>1.130788815213389</v>
+        <v>0.9282995970976597</v>
       </c>
       <c r="E13">
-        <v>-0.00332470122766689</v>
+        <v>-0.1038915557609943</v>
       </c>
       <c r="F13">
-        <v>-0.6475321466941368</v>
+        <v>-0.5601650417379405</v>
       </c>
       <c r="G13">
-        <v>-0.3585707796121328</v>
+        <v>-0.4611116163163456</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.2844862543937555</v>
+        <v>1.150868438032686</v>
       </c>
       <c r="D14">
-        <v>-1.190695441170871</v>
+        <v>-1.548742456340913</v>
       </c>
       <c r="E14">
-        <v>-0.940826012531005</v>
+        <v>-1.151069840634091</v>
       </c>
       <c r="F14">
-        <v>0.9336525919571101</v>
+        <v>0.8919892468831386</v>
       </c>
       <c r="G14">
-        <v>-1.026575510571312</v>
+        <v>-0.01800782502219997</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-1.614332701556931</v>
+        <v>-1.477293662123702</v>
       </c>
       <c r="D15">
-        <v>-0.9621181694679224</v>
+        <v>-1.210170955714605</v>
       </c>
       <c r="E15">
-        <v>-1.529450066586521</v>
+        <v>-1.443183749809393</v>
       </c>
       <c r="F15">
-        <v>0.1958955179460102</v>
+        <v>0.466039533068963</v>
       </c>
       <c r="G15">
-        <v>-0.87904572592466</v>
+        <v>-0.9620933173008346</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.386356039602025</v>
+        <v>-0.6550440709323352</v>
       </c>
       <c r="D16">
-        <v>1.218348315876945</v>
+        <v>1.196481552747584</v>
       </c>
       <c r="E16">
-        <v>0.8798151094800321</v>
+        <v>0.7895302756587472</v>
       </c>
       <c r="F16">
-        <v>-0.5192689687688168</v>
+        <v>-0.5254936144719552</v>
       </c>
       <c r="G16">
-        <v>-0.160688792480052</v>
+        <v>-0.1188981468837818</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>2.088471510816313</v>
+        <v>1.688443650389325</v>
       </c>
       <c r="D17">
-        <v>0.2436358508995303</v>
+        <v>0.8665724377768403</v>
       </c>
       <c r="E17">
-        <v>3.521512584613645</v>
+        <v>3.699474928478613</v>
       </c>
       <c r="F17">
-        <v>2.479969991418783</v>
+        <v>2.496879547419395</v>
       </c>
       <c r="G17">
-        <v>-0.1303712913791851</v>
+        <v>0.2814046702248297</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.530699304095071</v>
+        <v>0.3959144351401517</v>
       </c>
       <c r="D18">
-        <v>-0.2196798828375017</v>
+        <v>-0.01013979710712774</v>
       </c>
       <c r="E18">
-        <v>0.8026221783193906</v>
+        <v>0.9128843136825899</v>
       </c>
       <c r="F18">
-        <v>-0.3726227021013605</v>
+        <v>-0.2067038284329309</v>
       </c>
       <c r="G18">
-        <v>-0.5058920371418982</v>
+        <v>-0.6670176525940632</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.2001214749253008</v>
+        <v>-0.3632737243547166</v>
       </c>
       <c r="D19">
-        <v>0.6526351195727895</v>
+        <v>0.6308857851176762</v>
       </c>
       <c r="E19">
-        <v>-1.174503492586416</v>
+        <v>-1.126660546142085</v>
       </c>
       <c r="F19">
-        <v>-0.1495943016478149</v>
+        <v>0.1302592930882712</v>
       </c>
       <c r="G19">
-        <v>-0.9457259992549956</v>
+        <v>-1.066479966238278</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>2.074228879294891</v>
+        <v>2.236476488084529</v>
       </c>
       <c r="D20">
-        <v>-1.139778415254322</v>
+        <v>-0.7720041197805912</v>
       </c>
       <c r="E20">
-        <v>0.6191188357119722</v>
+        <v>0.7567414631357448</v>
       </c>
       <c r="F20">
-        <v>0.0409682508168513</v>
+        <v>-0.03480861744990223</v>
       </c>
       <c r="G20">
-        <v>0.5400913572107005</v>
+        <v>0.3734256300698625</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.1448754713018373</v>
+        <v>-0.6338620618577354</v>
       </c>
       <c r="D21">
-        <v>2.800282792255279</v>
+        <v>2.769477823883316</v>
       </c>
       <c r="E21">
-        <v>0.9663164572967696</v>
+        <v>0.7619061170130843</v>
       </c>
       <c r="F21">
-        <v>0.5116412062982862</v>
+        <v>0.4463051980376282</v>
       </c>
       <c r="G21">
-        <v>-0.421657507799614</v>
+        <v>0.1386251405832827</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-1.626182200666803</v>
+        <v>-1.79903120182813</v>
       </c>
       <c r="D22">
-        <v>0.9428886337010174</v>
+        <v>0.6995399503917505</v>
       </c>
       <c r="E22">
-        <v>0.852550568352754</v>
+        <v>0.7044747582820139</v>
       </c>
       <c r="F22">
-        <v>-0.4231102475630861</v>
+        <v>-0.5293084581046288</v>
       </c>
       <c r="G22">
-        <v>0.3062939313102174</v>
+        <v>0.2972716220502873</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.6195729646459136</v>
+        <v>0.7469756573710686</v>
       </c>
       <c r="D23">
-        <v>-2.425587590503658</v>
+        <v>-2.082034065356057</v>
       </c>
       <c r="E23">
-        <v>2.035125509596694</v>
+        <v>2.306778153766147</v>
       </c>
       <c r="F23">
-        <v>-0.5870634993621958</v>
+        <v>-0.3496916076760169</v>
       </c>
       <c r="G23">
-        <v>-0.6251378811181951</v>
+        <v>-0.9365203773843197</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-2.25320531510804</v>
+        <v>-2.400029107693251</v>
       </c>
       <c r="D24">
-        <v>1.964817633971202</v>
+        <v>1.441960682445332</v>
       </c>
       <c r="E24">
-        <v>0.1024598502103197</v>
+        <v>-0.3348730930956359</v>
       </c>
       <c r="F24">
-        <v>-1.753798077879982</v>
+        <v>-2.813860285399946</v>
       </c>
       <c r="G24">
-        <v>4.565813317935849</v>
+        <v>3.952393550702598</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.7831651658024216</v>
+        <v>-0.7376858113665269</v>
       </c>
       <c r="D25">
-        <v>-1.067806114824731</v>
+        <v>-1.069278456454431</v>
       </c>
       <c r="E25">
-        <v>1.703471816879339</v>
+        <v>1.728365729251886</v>
       </c>
       <c r="F25">
-        <v>-1.503175106791936</v>
+        <v>-1.585329268504456</v>
       </c>
       <c r="G25">
-        <v>0.5557158155562067</v>
+        <v>0.1341731914063247</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-1.769609914411626</v>
+        <v>-1.679288149192221</v>
       </c>
       <c r="D26">
-        <v>-0.7239542878979516</v>
+        <v>-0.9754753305788882</v>
       </c>
       <c r="E26">
-        <v>-0.03931769878749445</v>
+        <v>-0.04994430772956469</v>
       </c>
       <c r="F26">
-        <v>0.3194689641440414</v>
+        <v>0.3341956470581484</v>
       </c>
       <c r="G26">
-        <v>-0.2075722292496757</v>
+        <v>-0.04483015747233243</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.1431543103635687</v>
+        <v>-0.4227285725857871</v>
       </c>
       <c r="D27">
-        <v>1.82980281261597</v>
+        <v>1.730062562110114</v>
       </c>
       <c r="E27">
-        <v>-2.155133106688512</v>
+        <v>-2.202013659999908</v>
       </c>
       <c r="F27">
-        <v>-1.675919296349388</v>
+        <v>-1.462564384986774</v>
       </c>
       <c r="G27">
-        <v>-0.3258738924277445</v>
+        <v>-0.9526210055731714</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>1.928618899158616</v>
+        <v>2.819488174710003</v>
       </c>
       <c r="D28">
-        <v>-2.07960429785743</v>
+        <v>-2.078278690689132</v>
       </c>
       <c r="E28">
-        <v>0.8502072921281248</v>
+        <v>0.690273282861622</v>
       </c>
       <c r="F28">
-        <v>-1.578527430082852</v>
+        <v>-2.026287333540451</v>
       </c>
       <c r="G28">
-        <v>1.274765982598945</v>
+        <v>1.357661069033521</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.980020246958708</v>
+        <v>-2.400759392933219</v>
       </c>
       <c r="D29">
-        <v>3.276335353356722</v>
+        <v>2.84108769241589</v>
       </c>
       <c r="E29">
-        <v>0.5080004178327607</v>
+        <v>0.09120428510985919</v>
       </c>
       <c r="F29">
-        <v>-0.05170641987441976</v>
+        <v>-0.7173552233158824</v>
       </c>
       <c r="G29">
-        <v>2.570252841178055</v>
+        <v>2.544671430444016</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.2977939065118249</v>
+        <v>-0.5109540717986834</v>
       </c>
       <c r="D30">
-        <v>0.9253589583929829</v>
+        <v>0.8980995689466639</v>
       </c>
       <c r="E30">
-        <v>-0.5617354998996114</v>
+        <v>-0.5566758943823941</v>
       </c>
       <c r="F30">
-        <v>-0.5436065797643344</v>
+        <v>-0.3088325052654578</v>
       </c>
       <c r="G30">
-        <v>-0.8038284038777723</v>
+        <v>-0.9708743040708994</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.6311532344334724</v>
+        <v>0.5083408277942773</v>
       </c>
       <c r="D31">
-        <v>0.3592640058742014</v>
+        <v>0.4575601523151877</v>
       </c>
       <c r="E31">
-        <v>-1.914372798683122</v>
+        <v>-1.807866705795726</v>
       </c>
       <c r="F31">
-        <v>-1.342930023485941</v>
+        <v>-1.113650584545407</v>
       </c>
       <c r="G31">
-        <v>-0.2771162169649992</v>
+        <v>-0.9163819372057486</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>-1.56740497039669</v>
+        <v>-1.784847496028044</v>
       </c>
       <c r="D32">
-        <v>1.529079586820322</v>
+        <v>1.230614445158921</v>
       </c>
       <c r="E32">
-        <v>-0.7467611122349074</v>
+        <v>-0.8753959270631227</v>
       </c>
       <c r="F32">
-        <v>0.5881646765324703</v>
+        <v>0.7716623370794716</v>
       </c>
       <c r="G32">
-        <v>-1.237414127267997</v>
+        <v>-0.7646436795122542</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.5457671558375843</v>
+        <v>-0.4526824800546206</v>
       </c>
       <c r="D33">
-        <v>-0.2510535500074325</v>
+        <v>-0.3793746663693651</v>
       </c>
       <c r="E33">
-        <v>-1.133237566489232</v>
+        <v>-1.101800169210432</v>
       </c>
       <c r="F33">
-        <v>1.535237938391886</v>
+        <v>1.701685319382578</v>
       </c>
       <c r="G33">
-        <v>-0.9658836547169591</v>
+        <v>-0.479583242765153</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.953452427282499</v>
+        <v>2.332473369497436</v>
       </c>
       <c r="D34">
-        <v>-0.6470429154051638</v>
+        <v>-0.4906074587565096</v>
       </c>
       <c r="E34">
-        <v>0.6475747286190677</v>
+        <v>0.5766233161944156</v>
       </c>
       <c r="F34">
-        <v>-0.2665285542580233</v>
+        <v>-0.585879287831499</v>
       </c>
       <c r="G34">
-        <v>1.118990819595224</v>
+        <v>1.158333121467975</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.1363657164759434</v>
+        <v>-0.46400319170076</v>
       </c>
       <c r="D35">
-        <v>1.365960602690794</v>
+        <v>1.411457892503412</v>
       </c>
       <c r="E35">
-        <v>1.01056156291957</v>
+        <v>0.9582189676482979</v>
       </c>
       <c r="F35">
-        <v>0.5513060290180831</v>
+        <v>0.6168204934926242</v>
       </c>
       <c r="G35">
-        <v>-0.4850137493422474</v>
+        <v>-0.2467129904753848</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.4545623172232885</v>
+        <v>0.8857899756007958</v>
       </c>
       <c r="D36">
-        <v>-1.225234278592479</v>
+        <v>-1.282290697912024</v>
       </c>
       <c r="E36">
-        <v>-0.2113803167704824</v>
+        <v>-0.2401836029394132</v>
       </c>
       <c r="F36">
-        <v>1.365225681522773</v>
+        <v>1.108794840995963</v>
       </c>
       <c r="G36">
-        <v>0.7691323420353381</v>
+        <v>1.152598437769841</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-1.695562818408902</v>
+        <v>-1.5662871982809</v>
       </c>
       <c r="D37">
-        <v>-1.177504317991542</v>
+        <v>-1.381257699433706</v>
       </c>
       <c r="E37">
-        <v>-0.01773229839838623</v>
+        <v>0.04988229989725747</v>
       </c>
       <c r="F37">
-        <v>0.5651414800585901</v>
+        <v>0.8623649766233284</v>
       </c>
       <c r="G37">
-        <v>-1.563032319621478</v>
+        <v>-1.16994441785802</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.4305801649955896</v>
+        <v>0.04574018377263044</v>
       </c>
       <c r="D38">
-        <v>-0.5168224425206518</v>
+        <v>-0.8012345529952991</v>
       </c>
       <c r="E38">
-        <v>0.4914047360483497</v>
+        <v>0.3048373801470263</v>
       </c>
       <c r="F38">
-        <v>0.4686424052738588</v>
+        <v>0.5040426463255665</v>
       </c>
       <c r="G38">
-        <v>-1.304517887011377</v>
+        <v>-0.3917216744093349</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.4222122626689951</v>
+        <v>0.409160262761813</v>
       </c>
       <c r="D39">
-        <v>-0.6107710622258953</v>
+        <v>-0.4799028830555282</v>
       </c>
       <c r="E39">
-        <v>-0.6598718140173243</v>
+        <v>-0.5281766966799541</v>
       </c>
       <c r="F39">
-        <v>-1.298946595367539</v>
+        <v>-1.176653686090065</v>
       </c>
       <c r="G39">
-        <v>0.1049860403969301</v>
+        <v>-0.509905082919403</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.1325799175405022</v>
+        <v>-0.3752207015222777</v>
       </c>
       <c r="D40">
-        <v>3.002223353072304</v>
+        <v>2.981062568035953</v>
       </c>
       <c r="E40">
-        <v>-0.6868565622996844</v>
+        <v>-0.8131717817944391</v>
       </c>
       <c r="F40">
-        <v>0.01115939311716622</v>
+        <v>0.2210655513497004</v>
       </c>
       <c r="G40">
-        <v>-1.094696830096989</v>
+        <v>-0.8960221043690515</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.5272903394525239</v>
+        <v>-0.7675700618533364</v>
       </c>
       <c r="D41">
-        <v>0.4654711310086961</v>
+        <v>0.5287272525025062</v>
       </c>
       <c r="E41">
-        <v>2.548492046230358</v>
+        <v>2.514609895637651</v>
       </c>
       <c r="F41">
-        <v>-0.5873309068637097</v>
+        <v>-0.4976550764286256</v>
       </c>
       <c r="G41">
-        <v>-0.6150283100824155</v>
+        <v>-0.5398852203370403</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>2.90322278972689</v>
+        <v>2.833346819076852</v>
       </c>
       <c r="D42">
-        <v>-0.6370926047573731</v>
+        <v>-0.08275983759893768</v>
       </c>
       <c r="E42">
-        <v>-0.7994495607957699</v>
+        <v>-0.5354555589395471</v>
       </c>
       <c r="F42">
-        <v>0.2680177123966903</v>
+        <v>0.2844647426827752</v>
       </c>
       <c r="G42">
-        <v>0.6950959078889376</v>
+        <v>0.2104169169487169</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-1.493554205553412</v>
+        <v>-1.381279202983619</v>
       </c>
       <c r="D43">
-        <v>-1.426593741389257</v>
+        <v>-1.528065692659512</v>
       </c>
       <c r="E43">
-        <v>1.636114636129222</v>
+        <v>1.699380643664956</v>
       </c>
       <c r="F43">
-        <v>-0.8018380920113358</v>
+        <v>-0.5436568923015042</v>
       </c>
       <c r="G43">
-        <v>-1.238530537756243</v>
+        <v>-1.205436896272279</v>
       </c>
     </row>
     <row r="44">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.08295083368889461</v>
+        <v>0.1482908028368977</v>
       </c>
       <c r="D44">
-        <v>-2.608935113672662</v>
+        <v>-2.44460790672541</v>
       </c>
       <c r="E44">
-        <v>1.271062720789645</v>
+        <v>1.470339071628516</v>
       </c>
       <c r="F44">
-        <v>-3.757802244089647</v>
+        <v>-3.59134234372091</v>
       </c>
       <c r="G44">
-        <v>0.0986804471776665</v>
+        <v>-1.034418669959248</v>
       </c>
     </row>
     <row r="45">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.5920313062201294</v>
+        <v>0.4152777864638258</v>
       </c>
       <c r="D45">
-        <v>0.2149352652687446</v>
+        <v>0.4170084503153166</v>
       </c>
       <c r="E45">
-        <v>1.140608721205443</v>
+        <v>1.20224732312535</v>
       </c>
       <c r="F45">
-        <v>-0.3491851082249448</v>
+        <v>-0.1971325579109738</v>
       </c>
       <c r="G45">
-        <v>-0.607693026312887</v>
+        <v>-0.6580006760912253</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-2.480173458843234</v>
+        <v>-2.090904842724254</v>
       </c>
       <c r="D46">
-        <v>-1.519071037261191</v>
+        <v>-1.993127579985964</v>
       </c>
       <c r="E46">
-        <v>-0.9306234767737344</v>
+        <v>-0.9893314199031329</v>
       </c>
       <c r="F46">
-        <v>-0.08384344556322514</v>
+        <v>-0.1539738191996654</v>
       </c>
       <c r="G46">
-        <v>0.175204010492098</v>
+        <v>0.2383841155333191</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>2.587441334474506</v>
+        <v>2.216154402304308</v>
       </c>
       <c r="D47">
-        <v>1.076040907478348</v>
+        <v>1.585362894848891</v>
       </c>
       <c r="E47">
-        <v>0.07220318886746852</v>
+        <v>0.20205246147111</v>
       </c>
       <c r="F47">
-        <v>1.466891917704198</v>
+        <v>1.351294474675134</v>
       </c>
       <c r="G47">
-        <v>0.8876693696310842</v>
+        <v>0.8063507914099076</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>3.835637833518924</v>
+        <v>4.336210602931201</v>
       </c>
       <c r="D48">
-        <v>-0.7344246960078704</v>
+        <v>-0.3728905252854994</v>
       </c>
       <c r="E48">
-        <v>-0.6149907052582179</v>
+        <v>-0.6285606154746386</v>
       </c>
       <c r="F48">
-        <v>0.2671971811523407</v>
+        <v>-0.1281042095862382</v>
       </c>
       <c r="G48">
-        <v>1.576059074922017</v>
+        <v>1.599256675478977</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.09653691856878488</v>
+        <v>-0.3704956879410636</v>
       </c>
       <c r="D49">
-        <v>0.9462916141053307</v>
+        <v>1.015502216450743</v>
       </c>
       <c r="E49">
-        <v>1.064207974349252</v>
+        <v>1.051536668840506</v>
       </c>
       <c r="F49">
-        <v>-0.3019661347496588</v>
+        <v>-0.04294762960476543</v>
       </c>
       <c r="G49">
-        <v>-1.415912171917973</v>
+        <v>-1.17348324605912</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.002715005747397553</v>
+        <v>-0.03364458785539194</v>
       </c>
       <c r="D50">
-        <v>-0.7769198469199292</v>
+        <v>-0.653752513278271</v>
       </c>
       <c r="E50">
-        <v>0.5434731893468417</v>
+        <v>0.6751882513444432</v>
       </c>
       <c r="F50">
-        <v>-0.07779517561473845</v>
+        <v>0.1103032628231024</v>
       </c>
       <c r="G50">
-        <v>-0.5741574500727007</v>
+        <v>-0.7002438623854595</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.125588702339547</v>
+        <v>0.2075555411665304</v>
       </c>
       <c r="D51">
-        <v>-3.064958499233619</v>
+        <v>-2.927253077443043</v>
       </c>
       <c r="E51">
-        <v>-0.02815076241938808</v>
+        <v>0.2788726579451614</v>
       </c>
       <c r="F51">
-        <v>-0.5976816463083223</v>
+        <v>-0.2728815137791177</v>
       </c>
       <c r="G51">
-        <v>-0.638876329129455</v>
+        <v>-1.178087229168236</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>2.125777835264417</v>
+        <v>2.031573956257174</v>
       </c>
       <c r="D52">
-        <v>-0.941667421988358</v>
+        <v>-0.4347984329975788</v>
       </c>
       <c r="E52">
-        <v>0.3179490564222468</v>
+        <v>0.5839616387485372</v>
       </c>
       <c r="F52">
-        <v>-0.09629699886193718</v>
+        <v>0.003899384043846141</v>
       </c>
       <c r="G52">
-        <v>0.2814507142224854</v>
+        <v>-0.20934315093</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>1.359374722984867</v>
+        <v>1.207593978383835</v>
       </c>
       <c r="D53">
-        <v>-0.5184009437548988</v>
+        <v>-0.1216115720883633</v>
       </c>
       <c r="E53">
-        <v>1.653485308021829</v>
+        <v>1.808328473040988</v>
       </c>
       <c r="F53">
-        <v>1.777944147197805</v>
+        <v>1.724144255873164</v>
       </c>
       <c r="G53">
-        <v>0.1096532887730846</v>
+        <v>0.4665981460110319</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.566399024007632</v>
+        <v>-0.8008052078502734</v>
       </c>
       <c r="D54">
-        <v>1.11352023928285</v>
+        <v>1.04716281504884</v>
       </c>
       <c r="E54">
-        <v>0.360592176215264</v>
+        <v>0.2886813763209112</v>
       </c>
       <c r="F54">
-        <v>-0.00778195061055119</v>
+        <v>0.06722620458283424</v>
       </c>
       <c r="G54">
-        <v>-0.5676096968437425</v>
+        <v>-0.3739617921787141</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.387459949435929</v>
+        <v>-0.4474732224013402</v>
       </c>
       <c r="D55">
-        <v>-0.08068743532755907</v>
+        <v>-0.08214944059789586</v>
       </c>
       <c r="E55">
-        <v>2.066600215090343</v>
+        <v>1.927588328178805</v>
       </c>
       <c r="F55">
-        <v>0.7506692472710655</v>
+        <v>-0.1813756706788446</v>
       </c>
       <c r="G55">
-        <v>3.933024593730223</v>
+        <v>3.817714771062159</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>1.810482405964905</v>
+        <v>1.717334271935392</v>
       </c>
       <c r="D56">
-        <v>-0.5832600432555763</v>
+        <v>-0.1627479328124106</v>
       </c>
       <c r="E56">
-        <v>0.777859263960368</v>
+        <v>0.9493741408022084</v>
       </c>
       <c r="F56">
-        <v>0.1030800628979003</v>
+        <v>0.07377525738886653</v>
       </c>
       <c r="G56">
-        <v>0.4894406636476153</v>
+        <v>0.2405004540381146</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>1.891925110234598</v>
+        <v>1.886056239389541</v>
       </c>
       <c r="D57">
-        <v>-0.9806170050021581</v>
+        <v>-0.5976203064984604</v>
       </c>
       <c r="E57">
-        <v>-1.577065233734025</v>
+        <v>-1.302026459206084</v>
       </c>
       <c r="F57">
-        <v>-0.3437500828724284</v>
+        <v>-0.1754835525392062</v>
       </c>
       <c r="G57">
-        <v>0.1561787047092739</v>
+        <v>-0.4565321746181136</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.03071897581346719</v>
+        <v>-0.06282564949874382</v>
       </c>
       <c r="D58">
-        <v>-0.4866027314387584</v>
+        <v>-0.3465837894358655</v>
       </c>
       <c r="E58">
-        <v>0.5928371252551898</v>
+        <v>0.7341309958511141</v>
       </c>
       <c r="F58">
-        <v>-1.564271390459851</v>
+        <v>-1.146147218472271</v>
       </c>
       <c r="G58">
-        <v>-1.351278707580058</v>
+        <v>-1.803356876700126</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>2.131834354716875</v>
+        <v>2.351430594262353</v>
       </c>
       <c r="D59">
-        <v>-3.552171653349823</v>
+        <v>-2.913792064826454</v>
       </c>
       <c r="E59">
-        <v>1.617566619639654</v>
+        <v>2.051966059483596</v>
       </c>
       <c r="F59">
-        <v>-0.45765948099681</v>
+        <v>-0.3632969532228357</v>
       </c>
       <c r="G59">
-        <v>0.3564347166578511</v>
+        <v>-0.2169749191435487</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>2.489736463593748</v>
+        <v>2.762001355534941</v>
       </c>
       <c r="D60">
-        <v>-0.8319659161858137</v>
+        <v>-0.5178779564113216</v>
       </c>
       <c r="E60">
-        <v>-0.01795943959016542</v>
+        <v>0.03883417107896982</v>
       </c>
       <c r="F60">
-        <v>-0.1216007608321208</v>
+        <v>-0.3161907374962525</v>
       </c>
       <c r="G60">
-        <v>0.8778651927286809</v>
+        <v>0.780112847063133</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.547758960654344</v>
+        <v>-1.807342626917575</v>
       </c>
       <c r="D61">
-        <v>2.007720711823172</v>
+        <v>1.686850476237424</v>
       </c>
       <c r="E61">
-        <v>0.1322189467719539</v>
+        <v>-0.1232021554816705</v>
       </c>
       <c r="F61">
-        <v>-0.9294834464825018</v>
+        <v>-1.127157625154539</v>
       </c>
       <c r="G61">
-        <v>0.5638206108494389</v>
+        <v>0.5513227398930208</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.05032599810408053</v>
+        <v>-0.1132525125080392</v>
       </c>
       <c r="D62">
-        <v>0.2697599961107268</v>
+        <v>0.2391614207647963</v>
       </c>
       <c r="E62">
-        <v>-1.388572589499197</v>
+        <v>-1.363793410616594</v>
       </c>
       <c r="F62">
-        <v>-1.282551821383173</v>
+        <v>-1.225568698600071</v>
       </c>
       <c r="G62">
-        <v>0.2572931042233182</v>
+        <v>-0.2823875962878857</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.7463395485979035</v>
+        <v>0.395008093189036</v>
       </c>
       <c r="D63">
-        <v>1.626861105477901</v>
+        <v>1.765617021486599</v>
       </c>
       <c r="E63">
-        <v>-0.55073853999547</v>
+        <v>-0.5413329118150904</v>
       </c>
       <c r="F63">
-        <v>0.8608196858713737</v>
+        <v>1.006167846576003</v>
       </c>
       <c r="G63">
-        <v>-0.6541849312033112</v>
+        <v>-0.4492926666340341</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>2.3030740173315</v>
+        <v>2.228187044307289</v>
       </c>
       <c r="D64">
-        <v>-0.2556826737404539</v>
+        <v>0.1562163997922407</v>
       </c>
       <c r="E64">
-        <v>-1.361806228739506</v>
+        <v>-1.142389581005778</v>
       </c>
       <c r="F64">
-        <v>1.420678587076384</v>
+        <v>1.517020003087572</v>
       </c>
       <c r="G64">
-        <v>-0.04529262503531556</v>
+        <v>-0.0305820767084502</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>3.648631560487245</v>
+        <v>3.874428594990037</v>
       </c>
       <c r="D65">
-        <v>-2.151484794923416</v>
+        <v>-1.496042797719765</v>
       </c>
       <c r="E65">
-        <v>-1.351450743369681</v>
+        <v>-0.9691337358978636</v>
       </c>
       <c r="F65">
-        <v>0.5361857415251998</v>
+        <v>0.5104556329389274</v>
       </c>
       <c r="G65">
-        <v>1.194383183648506</v>
+        <v>0.517141371180313</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.2227367028970157</v>
+        <v>0.1406197219736557</v>
       </c>
       <c r="D66">
-        <v>-0.5367882022765263</v>
+        <v>-0.3623607109804633</v>
       </c>
       <c r="E66">
-        <v>1.194001773565668</v>
+        <v>1.306677326371274</v>
       </c>
       <c r="F66">
-        <v>1.251404453317703</v>
+        <v>1.427050432567783</v>
       </c>
       <c r="G66">
-        <v>-1.047519684673522</v>
+        <v>-0.5829317243042438</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>1.382813390309055</v>
+        <v>1.151558410305823</v>
       </c>
       <c r="D67">
-        <v>0.953001138614221</v>
+        <v>1.17493725088693</v>
       </c>
       <c r="E67">
-        <v>-0.8845832928987344</v>
+        <v>-0.8554699313803148</v>
       </c>
       <c r="F67">
-        <v>-0.7281907492501161</v>
+        <v>-0.8627027270465959</v>
       </c>
       <c r="G67">
-        <v>1.026969558179885</v>
+        <v>0.5599753231761587</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.2145500172818351</v>
+        <v>-0.08544271061321142</v>
       </c>
       <c r="D68">
-        <v>1.744822665321943</v>
+        <v>1.738071268634809</v>
       </c>
       <c r="E68">
-        <v>-1.15913452176891</v>
+        <v>-1.213506560550673</v>
       </c>
       <c r="F68">
-        <v>-0.2160950225858022</v>
+        <v>-0.1044163071741808</v>
       </c>
       <c r="G68">
-        <v>-0.476974814787925</v>
+        <v>-0.4716903561160415</v>
       </c>
     </row>
     <row r="69">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.9613107032587818</v>
+        <v>0.8386599953334356</v>
       </c>
       <c r="D69">
-        <v>-0.265345063049673</v>
+        <v>-0.008101613439714226</v>
       </c>
       <c r="E69">
-        <v>-0.2266705093455169</v>
+        <v>-0.05867129537596474</v>
       </c>
       <c r="F69">
-        <v>0.7176542644476077</v>
+        <v>0.8727981201319327</v>
       </c>
       <c r="G69">
-        <v>-0.3147631266349329</v>
+        <v>-0.401526238347536</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>1.95690206457493</v>
+        <v>1.877832115071721</v>
       </c>
       <c r="D70">
-        <v>-0.4853307818422667</v>
+        <v>-0.08528558409473926</v>
       </c>
       <c r="E70">
-        <v>-0.4377998834409981</v>
+        <v>-0.2445337447041225</v>
       </c>
       <c r="F70">
-        <v>-0.6686977263366144</v>
+        <v>-0.6677719503860663</v>
       </c>
       <c r="G70">
-        <v>0.7939297700689303</v>
+        <v>0.1220346688837808</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.1965655957400324</v>
+        <v>-0.5394740855988055</v>
       </c>
       <c r="D71">
-        <v>1.913398319609906</v>
+        <v>1.869812644096615</v>
       </c>
       <c r="E71">
-        <v>-0.1107084441104491</v>
+        <v>-0.2164032115724876</v>
       </c>
       <c r="F71">
-        <v>0.4033498225254863</v>
+        <v>0.4285982003899671</v>
       </c>
       <c r="G71">
-        <v>-0.3787390113056249</v>
+        <v>-0.1145053786519487</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-4.356356562663269</v>
+        <v>-4.539485101351825</v>
       </c>
       <c r="D72">
-        <v>2.428582058475992</v>
+        <v>1.57029385026753</v>
       </c>
       <c r="E72">
-        <v>0.1613401718198585</v>
+        <v>-0.3137175049773528</v>
       </c>
       <c r="F72">
-        <v>3.599612891481097</v>
+        <v>2.98757476048945</v>
       </c>
       <c r="G72">
-        <v>1.27018238632008</v>
+        <v>2.619950661345187</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-7.718604383815078</v>
+        <v>-6.669619183695862</v>
       </c>
       <c r="D73">
-        <v>-4.93060120230859</v>
+        <v>-6.253669099100267</v>
       </c>
       <c r="E73">
-        <v>-1.016625969171751</v>
+        <v>-1.172479535910638</v>
       </c>
       <c r="F73">
-        <v>2.666588589676996</v>
+        <v>1.918228403393246</v>
       </c>
       <c r="G73">
-        <v>2.858118090083305</v>
+        <v>3.31724142743409</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.2072833177488491</v>
+        <v>-0.1143772772347529</v>
       </c>
       <c r="D74">
-        <v>1.232672720856785</v>
+        <v>1.3536324101197</v>
       </c>
       <c r="E74">
-        <v>2.146507618261829</v>
+        <v>2.047539115704761</v>
       </c>
       <c r="F74">
-        <v>0.8027032954385083</v>
+        <v>0.6520741141914576</v>
       </c>
       <c r="G74">
-        <v>-0.07972162760208107</v>
+        <v>0.521948391965094</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-2.916727768455741</v>
+        <v>-2.387471419172927</v>
       </c>
       <c r="D75">
-        <v>-3.116414089795814</v>
+        <v>-3.578308691474241</v>
       </c>
       <c r="E75">
-        <v>-2.421847999220778</v>
+        <v>-2.244465012596514</v>
       </c>
       <c r="F75">
-        <v>-0.1977854321418537</v>
+        <v>0.1656406671610217</v>
       </c>
       <c r="G75">
-        <v>-1.100485963410287</v>
+        <v>-1.333760041315664</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-3.499167012772824</v>
+        <v>-3.214982390104044</v>
       </c>
       <c r="D76">
-        <v>-1.251590681657597</v>
+        <v>-1.849852170349287</v>
       </c>
       <c r="E76">
-        <v>-0.7015830678172399</v>
+        <v>-0.8007248845781875</v>
       </c>
       <c r="F76">
-        <v>0.6974117447357491</v>
+        <v>0.483770267667513</v>
       </c>
       <c r="G76">
-        <v>0.778011394278378</v>
+        <v>0.9263921850672217</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.1624392106286633</v>
+        <v>-0.1700175630621883</v>
       </c>
       <c r="D77">
-        <v>1.768262722603912</v>
+        <v>1.787634053043936</v>
       </c>
       <c r="E77">
-        <v>-0.1977504257907908</v>
+        <v>-0.2790061412889446</v>
       </c>
       <c r="F77">
-        <v>-0.04603822410625486</v>
+        <v>-0.07578349483703979</v>
       </c>
       <c r="G77">
-        <v>0.106505071654752</v>
+        <v>0.102539946772146</v>
       </c>
     </row>
     <row r="78">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.82179842508351</v>
+        <v>0.7040131653336236</v>
       </c>
       <c r="D78">
-        <v>0.07097086043683611</v>
+        <v>0.2427494036110708</v>
       </c>
       <c r="E78">
-        <v>-1.201733111767312</v>
+        <v>-1.07230816120923</v>
       </c>
       <c r="F78">
-        <v>-0.2382401567685146</v>
+        <v>-0.1294980555615288</v>
       </c>
       <c r="G78">
-        <v>0.161503491698493</v>
+        <v>-0.2876461713571243</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.4920766053336235</v>
+        <v>-0.7390705507972136</v>
       </c>
       <c r="D79">
-        <v>1.267012245098334</v>
+        <v>1.202258609539834</v>
       </c>
       <c r="E79">
-        <v>0.7978347222553993</v>
+        <v>0.6657391973987322</v>
       </c>
       <c r="F79">
-        <v>-1.699906320845899</v>
+        <v>-1.819255901013059</v>
       </c>
       <c r="G79">
-        <v>0.5539457833098396</v>
+        <v>0.2060529573694063</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.1596586245528225</v>
+        <v>-0.4936177809295538</v>
       </c>
       <c r="D80">
-        <v>1.509501863756175</v>
+        <v>1.534992022946944</v>
       </c>
       <c r="E80">
-        <v>0.9795820324581831</v>
+        <v>0.8984805140841058</v>
       </c>
       <c r="F80">
-        <v>0.06089269727427633</v>
+        <v>0.09192285940695311</v>
       </c>
       <c r="G80">
-        <v>-0.3627729962812405</v>
+        <v>-0.1910173451008331</v>
       </c>
     </row>
     <row r="81">
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.01622939440955766</v>
+        <v>0.3823055552684769</v>
       </c>
       <c r="D81">
-        <v>0.8898184822216836</v>
+        <v>0.519778386992981</v>
       </c>
       <c r="E81">
-        <v>-1.127942858233192</v>
+        <v>-1.43383840817679</v>
       </c>
       <c r="F81">
-        <v>1.103258510701185</v>
+        <v>0.8698373225258111</v>
       </c>
       <c r="G81">
-        <v>-0.06065555302388964</v>
+        <v>0.8113123968820116</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.7486001298139825</v>
+        <v>0.654008331612851</v>
       </c>
       <c r="D82">
-        <v>-0.6537560069908108</v>
+        <v>-0.383873029427946</v>
       </c>
       <c r="E82">
-        <v>0.6514011077199057</v>
+        <v>0.8316894010995539</v>
       </c>
       <c r="F82">
-        <v>-0.1102690668159531</v>
+        <v>0.1562131120490419</v>
       </c>
       <c r="G82">
-        <v>-0.8512755903325802</v>
+        <v>-0.9999036648676071</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.1742547707542405</v>
+        <v>0.0347488878144709</v>
       </c>
       <c r="D83">
-        <v>-2.548192601395607</v>
+        <v>-2.392362945187375</v>
       </c>
       <c r="E83">
-        <v>0.6490544614373318</v>
+        <v>0.9073585075807635</v>
       </c>
       <c r="F83">
-        <v>-0.4870216820625809</v>
+        <v>-0.2565848727740626</v>
       </c>
       <c r="G83">
-        <v>-0.4565597018797958</v>
+        <v>-0.845378392538665</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-2.043375171374394</v>
+        <v>-1.915493883872965</v>
       </c>
       <c r="D84">
-        <v>-0.3853545853382637</v>
+        <v>-0.7779118368411341</v>
       </c>
       <c r="E84">
-        <v>-1.640250870256684</v>
+        <v>-1.702685602910563</v>
       </c>
       <c r="F84">
-        <v>-1.299450108370559</v>
+        <v>-1.438312371007366</v>
       </c>
       <c r="G84">
-        <v>1.115429624346499</v>
+        <v>0.4975544732086226</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>2.701819707689727</v>
+        <v>2.660100915954967</v>
       </c>
       <c r="D85">
-        <v>-1.019122523316895</v>
+        <v>-0.4843935734939727</v>
       </c>
       <c r="E85">
-        <v>-1.726731464038807</v>
+        <v>-1.38802272523879</v>
       </c>
       <c r="F85">
-        <v>0.4236668887060378</v>
+        <v>0.5356698778241705</v>
       </c>
       <c r="G85">
-        <v>0.5694821790352862</v>
+        <v>-0.05961257406078871</v>
       </c>
     </row>
     <row r="86">
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.660840234718088</v>
+        <v>3.927636512457186</v>
       </c>
       <c r="D86">
-        <v>-2.085374815893958</v>
+        <v>-2.194968087799314</v>
       </c>
       <c r="E86">
-        <v>0.3152280308312177</v>
+        <v>0.04864602490335349</v>
       </c>
       <c r="F86">
-        <v>0.349028667563612</v>
+        <v>-0.119787346410673</v>
       </c>
       <c r="G86">
-        <v>0.7457955201523205</v>
+        <v>1.565063596388053</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.5876809192514295</v>
+        <v>-0.8073903800899545</v>
       </c>
       <c r="D87">
-        <v>1.323212867680873</v>
+        <v>1.201241625711369</v>
       </c>
       <c r="E87">
-        <v>-0.5091884924767798</v>
+        <v>-0.6008362430517398</v>
       </c>
       <c r="F87">
-        <v>-0.04607227438443697</v>
+        <v>-0.007622349256917529</v>
       </c>
       <c r="G87">
-        <v>-0.3631573908886393</v>
+        <v>-0.212509032369674</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>3.710607312888591</v>
+        <v>4.947571595924446</v>
       </c>
       <c r="D88">
-        <v>-0.7246762243819574</v>
+        <v>-0.8519398701271076</v>
       </c>
       <c r="E88">
-        <v>-1.613156874095792</v>
+        <v>-1.98826006654541</v>
       </c>
       <c r="F88">
-        <v>-0.4582232954369789</v>
+        <v>-1.105452409190314</v>
       </c>
       <c r="G88">
-        <v>1.717179578505471</v>
+        <v>2.217494397253776</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.8351006702161037</v>
+        <v>-1.039417063827579</v>
       </c>
       <c r="D89">
-        <v>0.3549382089009669</v>
+        <v>0.3563020563274675</v>
       </c>
       <c r="E89">
-        <v>2.25290098589854</v>
+        <v>2.218935816606601</v>
       </c>
       <c r="F89">
-        <v>-1.298435217708467</v>
+        <v>-1.126598258796411</v>
       </c>
       <c r="G89">
-        <v>-0.8368865780758705</v>
+        <v>-0.9456257003949767</v>
       </c>
     </row>
     <row r="90">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.5710840481119954</v>
+        <v>-0.9325044820990825</v>
       </c>
       <c r="D90">
-        <v>2.066951096654791</v>
+        <v>1.962975174596518</v>
       </c>
       <c r="E90">
-        <v>-0.07257693485171357</v>
+        <v>-0.1937905802595867</v>
       </c>
       <c r="F90">
-        <v>-0.09300113559816051</v>
+        <v>0.0352486154091159</v>
       </c>
       <c r="G90">
-        <v>-0.7708212781156289</v>
+        <v>-0.5972016026294857</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.1246047183253094</v>
+        <v>-0.3257657755470357</v>
       </c>
       <c r="D91">
-        <v>0.9645777909981517</v>
+        <v>0.9440083427800103</v>
       </c>
       <c r="E91">
-        <v>-1.162979837308436</v>
+        <v>-1.132126708432824</v>
       </c>
       <c r="F91">
-        <v>-0.07068594650476319</v>
+        <v>0.2581946832092155</v>
       </c>
       <c r="G91">
-        <v>-1.269370443480498</v>
+        <v>-1.281460022155705</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.05469696248486669</v>
+        <v>-0.0209843201867501</v>
       </c>
       <c r="D92">
-        <v>-0.7606039366499743</v>
+        <v>-0.5820984583730552</v>
       </c>
       <c r="E92">
-        <v>1.57749345608154</v>
+        <v>1.7022705192609</v>
       </c>
       <c r="F92">
-        <v>0.5344593171895046</v>
+        <v>0.6919060122491176</v>
       </c>
       <c r="G92">
-        <v>-0.6925311994236929</v>
+        <v>-0.5563917399459763</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.7917602619681644</v>
+        <v>0.5786641821448927</v>
       </c>
       <c r="D93">
-        <v>0.5886314153410388</v>
+        <v>0.7802227862888566</v>
       </c>
       <c r="E93">
-        <v>0.07592619622261687</v>
+        <v>0.1405664661971158</v>
       </c>
       <c r="F93">
-        <v>-0.0540470563772707</v>
+        <v>0.04289949784622699</v>
       </c>
       <c r="G93">
-        <v>-0.1499856208084887</v>
+        <v>-0.3239805468814412</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-1.070301975371745</v>
+        <v>-1.596934778754652</v>
       </c>
       <c r="D94">
-        <v>3.619332824957266</v>
+        <v>3.35709240579969</v>
       </c>
       <c r="E94">
-        <v>0.1955205966614184</v>
+        <v>-0.1212896829524497</v>
       </c>
       <c r="F94">
-        <v>0.7466327381549634</v>
+        <v>0.660691849845101</v>
       </c>
       <c r="G94">
-        <v>-0.5212815897725979</v>
+        <v>0.2040809671593031</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-3.418664989026673</v>
+        <v>-2.823901924993474</v>
       </c>
       <c r="D95">
-        <v>-3.497789422533778</v>
+        <v>-3.995558351595295</v>
       </c>
       <c r="E95">
-        <v>-0.3398793453520426</v>
+        <v>-0.232350181132409</v>
       </c>
       <c r="F95">
-        <v>1.156909096577565</v>
+        <v>1.291945952700564</v>
       </c>
       <c r="G95">
-        <v>-0.6196224059959825</v>
+        <v>-0.366071244487071</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.4276175345208242</v>
+        <v>-0.4533153361201251</v>
       </c>
       <c r="D96">
-        <v>-0.3958081600707267</v>
+        <v>-0.4040012318102015</v>
       </c>
       <c r="E96">
-        <v>-0.332153854720753</v>
+        <v>-0.2487152772075421</v>
       </c>
       <c r="F96">
-        <v>0.02369071709927249</v>
+        <v>0.2439281331077846</v>
       </c>
       <c r="G96">
-        <v>-0.8418003131667815</v>
+        <v>-0.8415088011635662</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>1.645160795385248</v>
+        <v>1.637373871265473</v>
       </c>
       <c r="D97">
-        <v>-0.7363395826578573</v>
+        <v>-0.4321866693566356</v>
       </c>
       <c r="E97">
-        <v>-2.39982263849059</v>
+        <v>-2.134096375506274</v>
       </c>
       <c r="F97">
-        <v>-0.4929708752655481</v>
+        <v>-0.2687844088418478</v>
       </c>
       <c r="G97">
-        <v>0.08117245808525364</v>
+        <v>-0.6577831179576649</v>
       </c>
     </row>
     <row r="98">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-1.832261377962032</v>
+        <v>-1.656582632773973</v>
       </c>
       <c r="D98">
-        <v>-1.051864202755759</v>
+        <v>-1.353338401359978</v>
       </c>
       <c r="E98">
-        <v>-1.724097531157228</v>
+        <v>-1.655339263753036</v>
       </c>
       <c r="F98">
-        <v>-0.04953879074951772</v>
+        <v>0.1641928044943325</v>
       </c>
       <c r="G98">
-        <v>-0.5746053264952274</v>
+        <v>-0.7576371110269341</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.930100276628201</v>
+        <v>1.761533440960938</v>
       </c>
       <c r="D99">
-        <v>0.008555949151668449</v>
+        <v>0.4094235477726855</v>
       </c>
       <c r="E99">
-        <v>0.4117517459569114</v>
+        <v>0.5199343678823256</v>
       </c>
       <c r="F99">
-        <v>1.562072615884629</v>
+        <v>1.241228927176711</v>
       </c>
       <c r="G99">
-        <v>1.47632327553297</v>
+        <v>1.573204113036838</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.187276288702045</v>
+        <v>-0.3608070530683505</v>
       </c>
       <c r="D100">
-        <v>0.9542782588886756</v>
+        <v>0.897771395603162</v>
       </c>
       <c r="E100">
-        <v>-1.10711414131642</v>
+        <v>-1.135422286108447</v>
       </c>
       <c r="F100">
-        <v>-1.446160349885028</v>
+        <v>-1.358547860689467</v>
       </c>
       <c r="G100">
-        <v>0.009237175671049203</v>
+        <v>-0.4695716377686636</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.3629987833044832</v>
+        <v>0.0432422428054146</v>
       </c>
       <c r="D101">
-        <v>1.282188850755241</v>
+        <v>1.402186009374423</v>
       </c>
       <c r="E101">
-        <v>0.74776159298498</v>
+        <v>0.7184649366669672</v>
       </c>
       <c r="F101">
-        <v>-0.1401451196839163</v>
+        <v>-0.1107572573225633</v>
       </c>
       <c r="G101">
-        <v>-0.130542265429455</v>
+        <v>-0.1506341786927839</v>
       </c>
     </row>
     <row r="102">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.6804496115905426</v>
+        <v>0.4556568141391863</v>
       </c>
       <c r="D102">
-        <v>0.3368466682233791</v>
+        <v>0.5669134124765902</v>
       </c>
       <c r="E102">
-        <v>1.272965869888173</v>
+        <v>1.32718036349408</v>
       </c>
       <c r="F102">
-        <v>0.8838937559258615</v>
+        <v>0.848792831600378</v>
       </c>
       <c r="G102">
-        <v>0.08304711639833484</v>
+        <v>0.2567098814037919</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>1.132423769824054</v>
+        <v>2.741253979505393</v>
       </c>
       <c r="D103">
-        <v>-0.6150047325801672</v>
+        <v>-1.367138133260293</v>
       </c>
       <c r="E103">
-        <v>-0.8837532785991097</v>
+        <v>-1.574669848566261</v>
       </c>
       <c r="F103">
-        <v>-1.241370947156764</v>
+        <v>-1.798442048982585</v>
       </c>
       <c r="G103">
-        <v>0.1662520414646139</v>
+        <v>1.389803746554801</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>1.644523702968532</v>
+        <v>1.467773172590264</v>
       </c>
       <c r="D104">
-        <v>0.5681456873498911</v>
+        <v>0.8208277740124917</v>
       </c>
       <c r="E104">
-        <v>-2.648598614004396</v>
+        <v>-2.479390293983588</v>
       </c>
       <c r="F104">
-        <v>-0.8115316553903672</v>
+        <v>-0.6037193407700902</v>
       </c>
       <c r="G104">
-        <v>0.09231182555388634</v>
+        <v>-0.6646821003601556</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>1.074642807562157</v>
+        <v>0.8965654185062839</v>
       </c>
       <c r="D105">
-        <v>0.4995260444883087</v>
+        <v>0.7039168855041456</v>
       </c>
       <c r="E105">
-        <v>-0.8665513271984839</v>
+        <v>-0.7745284551838525</v>
       </c>
       <c r="F105">
-        <v>-0.9625802735277982</v>
+        <v>-0.8823003224452476</v>
       </c>
       <c r="G105">
-        <v>0.3647422673228788</v>
+        <v>-0.2745462707279265</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-2.208612861262733</v>
+        <v>-2.156118088734448</v>
       </c>
       <c r="D106">
-        <v>0.01734915779672039</v>
+        <v>-0.3696631488073301</v>
       </c>
       <c r="E106">
-        <v>-0.1159766192168915</v>
+        <v>-0.2447933380883779</v>
       </c>
       <c r="F106">
-        <v>-0.4065383303726395</v>
+        <v>-0.545326652103987</v>
       </c>
       <c r="G106">
-        <v>0.5124102236247412</v>
+        <v>0.4604744585652096</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.3899569824668406</v>
+        <v>0.2378445583759018</v>
       </c>
       <c r="D107">
-        <v>0.6584555926158898</v>
+        <v>0.7344592433906477</v>
       </c>
       <c r="E107">
-        <v>0.0170560409164442</v>
+        <v>0.005082582244150161</v>
       </c>
       <c r="F107">
-        <v>-0.3947867408263688</v>
+        <v>-0.4119380681193259</v>
       </c>
       <c r="G107">
-        <v>0.1697906910331791</v>
+        <v>0.03215989519263893</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.4234646542086403</v>
+        <v>0.3250048583619537</v>
       </c>
       <c r="D108">
-        <v>0.1127816933326863</v>
+        <v>0.1984180142623376</v>
       </c>
       <c r="E108">
-        <v>-1.840683640569892</v>
+        <v>-1.702536811385458</v>
       </c>
       <c r="F108">
-        <v>-0.401981392010633</v>
+        <v>-0.1094446155990572</v>
       </c>
       <c r="G108">
-        <v>-0.6138424217070251</v>
+        <v>-1.042254861171988</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>1.179248584021267</v>
+        <v>0.9260939940822822</v>
       </c>
       <c r="D109">
-        <v>0.6446467680975099</v>
+        <v>0.9065044498398008</v>
       </c>
       <c r="E109">
-        <v>-0.6627749869384744</v>
+        <v>-0.5247135950674866</v>
       </c>
       <c r="F109">
-        <v>1.000068465876889</v>
+        <v>1.233245924504957</v>
       </c>
       <c r="G109">
-        <v>-0.7014884927668557</v>
+        <v>-0.6841651801181988</v>
       </c>
     </row>
     <row r="110">
@@ -3319,19 +3319,19 @@
         </is>
       </c>
       <c r="C110">
-        <v>-1.497844692880546</v>
+        <v>-1.315963592724809</v>
       </c>
       <c r="D110">
-        <v>-1.741409930408131</v>
+        <v>-1.871919621909736</v>
       </c>
       <c r="E110">
-        <v>0.9395918848526024</v>
+        <v>1.001666185473055</v>
       </c>
       <c r="F110">
-        <v>0.1993933661656235</v>
+        <v>0.07676389443468884</v>
       </c>
       <c r="G110">
-        <v>0.6855542411499267</v>
+        <v>0.5603310920416851</v>
       </c>
     </row>
     <row r="111">
@@ -3346,19 +3346,19 @@
         </is>
       </c>
       <c r="C111">
-        <v>1.243856572947172</v>
+        <v>0.9499486143437919</v>
       </c>
       <c r="D111">
-        <v>0.6285176514966959</v>
+        <v>0.9623261890490474</v>
       </c>
       <c r="E111">
-        <v>1.788358616151744</v>
+        <v>1.832709722300429</v>
       </c>
       <c r="F111">
-        <v>1.639524170703658</v>
+        <v>1.570675034837446</v>
       </c>
       <c r="G111">
-        <v>-0.1531200438461732</v>
+        <v>0.4111491372431054</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.2767921259678151</v>
+        <v>0.3012182429146693</v>
       </c>
       <c r="D112">
-        <v>-2.165743352758865</v>
+        <v>-1.810345462090538</v>
       </c>
       <c r="E112">
-        <v>3.249109740268692</v>
+        <v>3.513270825247824</v>
       </c>
       <c r="F112">
-        <v>0.3061817999681476</v>
+        <v>0.5900920834842094</v>
       </c>
       <c r="G112">
-        <v>-0.9377050188427103</v>
+        <v>-1.032924993234864</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>0.990951003663656</v>
+        <v>0.7522337819280968</v>
       </c>
       <c r="D113">
-        <v>1.190257815226943</v>
+        <v>1.31953590901206</v>
       </c>
       <c r="E113">
-        <v>-1.744636834152962</v>
+        <v>-1.704400168239032</v>
       </c>
       <c r="F113">
-        <v>0.06687820881273975</v>
+        <v>0.1110046081568407</v>
       </c>
       <c r="G113">
-        <v>0.1983964965813689</v>
+        <v>-0.04315913615959285</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.9709451897192906</v>
+        <v>-0.4176812503114622</v>
       </c>
       <c r="D114">
-        <v>-2.152466353163687</v>
+        <v>-2.443149718721302</v>
       </c>
       <c r="E114">
-        <v>-3.195919810414642</v>
+        <v>-3.049959003110462</v>
       </c>
       <c r="F114">
-        <v>1.434040046430801</v>
+        <v>1.814873036544138</v>
       </c>
       <c r="G114">
-        <v>-1.586177073430586</v>
+        <v>-1.252825712987117</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-2.487430439008234</v>
+        <v>-2.172300290906855</v>
       </c>
       <c r="D115">
-        <v>-2.886128952316267</v>
+        <v>-3.079887043953754</v>
       </c>
       <c r="E115">
-        <v>3.085246496578513</v>
+        <v>3.145540078697891</v>
       </c>
       <c r="F115">
-        <v>-3.051003599846906</v>
+        <v>-2.765859582924821</v>
       </c>
       <c r="G115">
-        <v>-1.45399549872841</v>
+        <v>-1.698499290452875</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.655089130246827</v>
+        <v>-1.495636129385886</v>
       </c>
       <c r="D116">
-        <v>-0.9388275718153141</v>
+        <v>-1.192265329226655</v>
       </c>
       <c r="E116">
-        <v>0.3092276121503665</v>
+        <v>0.2544488310818924</v>
       </c>
       <c r="F116">
-        <v>-1.283646716538289</v>
+        <v>-1.427690294140877</v>
       </c>
       <c r="G116">
-        <v>0.6580409740092108</v>
+        <v>0.3831158208833031</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-1.725542344911338</v>
+        <v>-1.927563976970878</v>
       </c>
       <c r="D117">
-        <v>1.549008941808705</v>
+        <v>1.215909479923758</v>
       </c>
       <c r="E117">
-        <v>-0.005462128393742105</v>
+        <v>-0.2252334219934503</v>
       </c>
       <c r="F117">
-        <v>1.015887490868089</v>
+        <v>0.628875219105935</v>
       </c>
       <c r="G117">
-        <v>1.415369393883473</v>
+        <v>1.626128350674778</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>1.928086612772548</v>
+        <v>1.806298194528247</v>
       </c>
       <c r="D118">
-        <v>-0.6654110962111668</v>
+        <v>-0.1947091623426197</v>
       </c>
       <c r="E118">
-        <v>1.29996371908064</v>
+        <v>1.470085715364723</v>
       </c>
       <c r="F118">
-        <v>1.794586492752021</v>
+        <v>1.598735450414922</v>
       </c>
       <c r="G118">
-        <v>0.7970324909446884</v>
+        <v>1.068456791875845</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>-1.719780368534306</v>
+        <v>-1.736801641752052</v>
       </c>
       <c r="D119">
-        <v>0.5679831591777741</v>
+        <v>0.2041704143951392</v>
       </c>
       <c r="E119">
-        <v>-2.157441538232904</v>
+        <v>-2.220998032071276</v>
       </c>
       <c r="F119">
-        <v>-1.103941985905112</v>
+        <v>-0.9478367743685023</v>
       </c>
       <c r="G119">
-        <v>-0.3270627994395012</v>
+        <v>-0.6977570397378938</v>
       </c>
     </row>
     <row r="120">
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.45674246113926</v>
+        <v>0.2915101088943</v>
       </c>
       <c r="D120">
-        <v>-0.1394254001708664</v>
+        <v>0.07277356031892938</v>
       </c>
       <c r="E120">
-        <v>0.5727958350397676</v>
+        <v>0.7265147461104533</v>
       </c>
       <c r="F120">
-        <v>1.71675330061941</v>
+        <v>2.035715155096988</v>
       </c>
       <c r="G120">
-        <v>-1.504920748429658</v>
+        <v>-1.038098086026974</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.1405871102720522</v>
+        <v>-0.3447578173433867</v>
       </c>
       <c r="D121">
-        <v>0.8391525413517219</v>
+        <v>0.8388876522849597</v>
       </c>
       <c r="E121">
-        <v>-0.6517082331721459</v>
+        <v>-0.6296118968401365</v>
       </c>
       <c r="F121">
-        <v>1.51980073524537</v>
+        <v>1.65319105622267</v>
       </c>
       <c r="G121">
-        <v>-0.7041544289877024</v>
+        <v>-0.3228052083964241</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-1.214672089520727</v>
+        <v>-1.40080284464883</v>
       </c>
       <c r="D122">
-        <v>0.4045411371041382</v>
+        <v>0.3267171211422746</v>
       </c>
       <c r="E122">
-        <v>2.110688029323779</v>
+        <v>2.050643670256195</v>
       </c>
       <c r="F122">
-        <v>-0.1638628488506555</v>
+        <v>-0.03321691811000078</v>
       </c>
       <c r="G122">
-        <v>-0.9545968697300451</v>
+        <v>-0.6791210167323337</v>
       </c>
     </row>
     <row r="123">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.9631855471952256</v>
+        <v>0.8290174279165382</v>
       </c>
       <c r="D123">
-        <v>0.7735006734832731</v>
+        <v>0.8911349570192637</v>
       </c>
       <c r="E123">
-        <v>-1.377209995357213</v>
+        <v>-1.33891035639256</v>
       </c>
       <c r="F123">
-        <v>0.619159790167094</v>
+        <v>0.6048282966415768</v>
       </c>
       <c r="G123">
-        <v>0.3270015219536707</v>
+        <v>0.2405458353282231</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.367333706667223</v>
+        <v>-1.510620393342876</v>
       </c>
       <c r="D124">
-        <v>0.6062073676045455</v>
+        <v>0.4195362476243811</v>
       </c>
       <c r="E124">
-        <v>0.19442131135778</v>
+        <v>0.1434174619656537</v>
       </c>
       <c r="F124">
-        <v>-0.07313116850185172</v>
+        <v>0.1126007671844668</v>
       </c>
       <c r="G124">
-        <v>-0.9428882420218879</v>
+        <v>-0.8032828341786751</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.8546209191122812</v>
+        <v>-0.8459622557472115</v>
       </c>
       <c r="D125">
-        <v>-0.3919732948977389</v>
+        <v>-0.4853713209410399</v>
       </c>
       <c r="E125">
-        <v>0.5057713420837492</v>
+        <v>0.4801368091418463</v>
       </c>
       <c r="F125">
-        <v>0.9455774211955992</v>
+        <v>0.7377322943692965</v>
       </c>
       <c r="G125">
-        <v>0.5940639704629456</v>
+        <v>0.9048054566903607</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-2.656786934020019</v>
+        <v>-2.337586350202472</v>
       </c>
       <c r="D126">
-        <v>-1.519811175834576</v>
+        <v>-2.001434391262966</v>
       </c>
       <c r="E126">
-        <v>-2.153479509300798</v>
+        <v>-2.141749544741044</v>
       </c>
       <c r="F126">
-        <v>0.5110718999120015</v>
+        <v>0.3964582242063094</v>
       </c>
       <c r="G126">
-        <v>0.8605014104949255</v>
+        <v>0.6548472279946823</v>
       </c>
     </row>
   </sheetData>
